--- a/manual_test/design/US-07_TestCases.xlsx
+++ b/manual_test/design/US-07_TestCases.xlsx
@@ -39,7 +39,7 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mge8gH7170EtjFHbdjdufy8sBDx5Q=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mil9O2QNzYdl/u5c6tBD0O7ZhC6MQ=="/>
     </ext>
   </extLst>
 </comments>
@@ -51,13 +51,13 @@
     <t xml:space="preserve">ID                                  </t>
   </si>
   <si>
-    <t>Connected ?</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
     <t>Règle métier</t>
+  </si>
+  <si>
+    <t>Connected ?</t>
   </si>
   <si>
     <t xml:space="preserve">RM-01                              </t>
@@ -75,13 +75,16 @@
     <t xml:space="preserve">RM-02                             </t>
   </si>
   <si>
+    <t>ID User Story</t>
+  </si>
+  <si>
     <t>Un compte voyageur existe</t>
   </si>
   <si>
-    <t>PRE-02</t>
+    <t xml:space="preserve">  Un Visiteur peut commencer la réservation mais ne peut pas la finaliser.</t>
   </si>
   <si>
-    <t xml:space="preserve">  Un Visiteur peut commencer la réservation mais ne peut pas la finaliser.</t>
+    <t>PRE-02</t>
   </si>
   <si>
     <t>Un compte hôte existe</t>
@@ -96,115 +99,79 @@
     <t xml:space="preserve"> La date de début doit être disponible et dans le futur.</t>
   </si>
   <si>
+    <t>ID Cas de test (Jira)</t>
+  </si>
+  <si>
     <t>Le voyageur peut se connecter</t>
   </si>
   <si>
     <t xml:space="preserve">RM-04                              </t>
   </si>
   <si>
+    <t>Titre  Cas de test</t>
+  </si>
+  <si>
     <t>PRE-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> La date de fin doit être être postérieure à la date de début et disponible.</t>
   </si>
   <si>
     <t>L'hôte a créé une annonce</t>
   </si>
   <si>
-    <t xml:space="preserve"> La date de fin doit être être postérieure à la date de début et disponible.</t>
+    <t>Règles métier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM-05                               </t>
+  </si>
+  <si>
+    <t>Priorité</t>
+  </si>
+  <si>
+    <t>Le nombre de voyageurs doit être un entier strictement positif.</t>
+  </si>
+  <si>
+    <t>Connected?</t>
+  </si>
+  <si>
+    <t>Les critères d'acceptation</t>
+  </si>
+  <si>
+    <t>Technique de conception</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM-06                               </t>
+  </si>
+  <si>
+    <t>Niveau de test</t>
+  </si>
+  <si>
+    <t>Vérifier l'affichage du message de confirmation.</t>
+  </si>
+  <si>
+    <t>Type de test</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Préconditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM-07                             </t>
+  </si>
+  <si>
+    <t>Données de test</t>
   </si>
   <si>
     <t>PRE-05</t>
   </si>
   <si>
-    <t xml:space="preserve">RM-05                               </t>
-  </si>
-  <si>
-    <t>L'annonce est active</t>
-  </si>
-  <si>
-    <t>Le nombre de voyageurs doit être un entier strictement positif.</t>
-  </si>
-  <si>
-    <t>PRE-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM-06                               </t>
-  </si>
-  <si>
-    <t>Connected?</t>
-  </si>
-  <si>
-    <t>Il y a des dates disponibles</t>
-  </si>
-  <si>
-    <t>Vérifier l'affichage du message de confirmation.</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>PRE-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM-07                             </t>
-  </si>
-  <si>
-    <t>Le voyageur a ouvert la page de l'annonce</t>
-  </si>
-  <si>
     <t>Une demande de réservation apparaît dans le tableau de bord de l'Hôte avec le statut « NOUVEAU ».</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>PRE-08</t>
-  </si>
-  <si>
-    <t>Le Voyageur est connecté.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RM-08                               </t>
-  </si>
-  <si>
-    <t>Les dates réservées deviennent indisponibles.</t>
-  </si>
-  <si>
-    <t>Available?</t>
-  </si>
-  <si>
-    <t>ID User Story</t>
-  </si>
-  <si>
-    <t>Titre User Story</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date valide? </t>
-  </si>
-  <si>
-    <t>Exigence</t>
-  </si>
-  <si>
-    <t>Priorité</t>
-  </si>
-  <si>
-    <t>Condition de test</t>
-  </si>
-  <si>
-    <t>Technique de conception</t>
-  </si>
-  <si>
-    <t>Niveau de test</t>
-  </si>
-  <si>
-    <t>Type de test</t>
-  </si>
-  <si>
-    <t>ID Cas de test (Jira)</t>
-  </si>
-  <si>
-    <t>Préconditions</t>
-  </si>
-  <si>
-    <t>Données de test</t>
   </si>
   <si>
     <t>Résultat attendu</t>
@@ -216,25 +183,55 @@
     <t>Script Robot Framework</t>
   </si>
   <si>
-    <t>Reservation créée ?</t>
+    <t>L'annonce est active</t>
   </si>
   <si>
     <t>Statut</t>
   </si>
   <si>
+    <t xml:space="preserve">RM-08                               </t>
+  </si>
+  <si>
     <t>Commentaires</t>
+  </si>
+  <si>
+    <t>Les dates réservées deviennent indisponibles.</t>
+  </si>
+  <si>
+    <t>Available?</t>
+  </si>
+  <si>
+    <t>PRE-06</t>
+  </si>
+  <si>
+    <t>Il y a des dates disponibles</t>
   </si>
   <si>
     <t>PP-07</t>
   </si>
   <si>
+    <t>PRE-07</t>
+  </si>
+  <si>
+    <t>Le voyageur a ouvert la page de l'annonce</t>
+  </si>
+  <si>
+    <t>PRE-08</t>
+  </si>
+  <si>
+    <t>PP-11</t>
+  </si>
+  <si>
+    <t>Le Voyageur est connecté.</t>
+  </si>
+  <si>
     <t>Faire une demande de réservation</t>
   </si>
   <si>
-    <t xml:space="preserve">Demande créée  </t>
+    <t>Seul un Voyageur connecté peut envoyer une demande de réservation</t>
   </si>
   <si>
-    <t>Seul un Voyageur connecté peut envoyer une demande de réservation</t>
+    <t xml:space="preserve">date valide? </t>
   </si>
   <si>
     <t>Haute</t>
@@ -246,16 +243,10 @@
     <t>Test basé sur les cas d'utilisation (Use Case Testing)</t>
   </si>
   <si>
-    <t>Message créé</t>
-  </si>
-  <si>
     <t>Test système</t>
   </si>
   <si>
     <t>Fonctionnel</t>
-  </si>
-  <si>
-    <t>PP-11</t>
   </si>
   <si>
     <t>PRE-01 à PRE-07</t>
@@ -276,6 +267,12 @@
     <t>Fait</t>
   </si>
   <si>
+    <t>Reservation créée ?</t>
+  </si>
+  <si>
+    <t>PP-12</t>
+  </si>
+  <si>
     <t>Un Visiteur ne peut pas finaliser une demande</t>
   </si>
   <si>
@@ -285,52 +282,28 @@
     <t>Table de décision</t>
   </si>
   <si>
-    <t>Annonce disponible</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>↓</t>
-  </si>
-  <si>
-    <t>Demande envoyée</t>
-  </si>
-  <si>
-    <t>PP-12</t>
-  </si>
-  <si>
-    <t>En attente</t>
-  </si>
-  <si>
     <t>PRE-04 à PRE-06</t>
   </si>
   <si>
-    <t>Acceptée</t>
+    <t xml:space="preserve">Demande créée  </t>
   </si>
   <si>
     <t>La demande de réservation n'est pas créée. Message d’error est afficher "Vous devez vous connecter pour effectuer une réservation"</t>
   </si>
   <si>
-    <t>Refusée</t>
-  </si>
-  <si>
-    <t>Réservation confirmée</t>
-  </si>
-  <si>
     <t>demande-voyageur_non_connecter.robot</t>
   </si>
   <si>
-    <t>Dates indisponibles</t>
+    <t>Message créé</t>
+  </si>
+  <si>
+    <t>PP-13</t>
   </si>
   <si>
     <t>Vérifier la validation des dates de début  réservation</t>
   </si>
   <si>
     <t>Partitionnement en classes d'équivalence</t>
-  </si>
-  <si>
-    <t>PP-13</t>
   </si>
   <si>
     <t>Date de début : une date antérieure à aujourd'hui ou déjà réservée.</t>
@@ -342,7 +315,10 @@
     <t>Non</t>
   </si>
   <si>
-    <t xml:space="preserve">Message de confirmation affiché </t>
+    <t>PP-14</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t xml:space="preserve"> La date de fin doit être disponible et dans le futur et &gt; de la date de début.</t>
@@ -352,9 +328,6 @@
   </si>
   <si>
     <t>Analyse des valeurs limites</t>
-  </si>
-  <si>
-    <t>PP-14</t>
   </si>
   <si>
     <t xml:space="preserve">Date début &lt;= Date fin 
@@ -367,22 +340,52 @@
     <t>validation_date_fin.robot</t>
   </si>
   <si>
+    <t>PP-18</t>
+  </si>
+  <si>
+    <t>Annonce disponible</t>
+  </si>
+  <si>
     <t>Vérifier la validation du nombre de voyageurs</t>
   </si>
   <si>
-    <t>PP-18</t>
+    <t>↓</t>
+  </si>
+  <si>
+    <t>Demande envoyée</t>
+  </si>
+  <si>
+    <t>En attente</t>
   </si>
   <si>
     <t>PRE-01 à PRE-08</t>
   </si>
   <si>
+    <t>Acceptée</t>
+  </si>
+  <si>
     <t>0</t>
+  </si>
+  <si>
+    <t>Refusée</t>
+  </si>
+  <si>
+    <t>Réservation confirmée</t>
   </si>
   <si>
     <t>La demande de réservation n'est pas créée. Message d’error est afficher "Veuillez choisir des voyageurs"</t>
   </si>
   <si>
+    <t>Dates indisponibles</t>
+  </si>
+  <si>
     <t>validation_Nb_voyageurs.robot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Message de confirmation affiché </t>
+  </si>
+  <si>
+    <t>PP-15</t>
   </si>
   <si>
     <t>Vérifier l'affichage du message de confirmation suite de réservation valide</t>
@@ -391,10 +394,10 @@
     <t>Error Guessing</t>
   </si>
   <si>
-    <t>PP-15</t>
+    <t>Un message apparaît  "Demande de réservation envoyée. Veuillez attendre la confirmation! ".</t>
   </si>
   <si>
-    <t>Un message apparaît  "Demande de réservation envoyée. Veuillez attendre la confirmation! ".</t>
+    <t>PP-16</t>
   </si>
   <si>
     <t xml:space="preserve">  Une réservation est créée le tableau de bord de l'Hôte</t>
@@ -406,9 +409,6 @@
     <t>Test basé sur les cas d'utilisation</t>
   </si>
   <si>
-    <t>PP-16</t>
-  </si>
-  <si>
     <t>PRE-04 à PRE-07</t>
   </si>
   <si>
@@ -418,10 +418,10 @@
     <t>creation_reservation_cote_hote.robot</t>
   </si>
   <si>
-    <t>Vérifier le blocage des dates réservées</t>
+    <t>PP-17</t>
   </si>
   <si>
-    <t>PP-17</t>
+    <t>Vérifier le blocage des dates réservées</t>
   </si>
   <si>
     <t>PRE-04 à PRE-08</t>
@@ -571,16 +571,13 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -588,28 +585,17 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -620,11 +606,18 @@
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -632,20 +625,27 @@
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -772,14 +772,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:P9" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="16">
     <tableColumn name="ID User Story" id="1"/>
-    <tableColumn name="Titre User Story" id="2"/>
-    <tableColumn name="Exigence" id="3"/>
-    <tableColumn name="Priorité" id="4"/>
-    <tableColumn name="Condition de test" id="5"/>
-    <tableColumn name="Technique de conception" id="6"/>
-    <tableColumn name="Niveau de test" id="7"/>
-    <tableColumn name="Type de test" id="8"/>
-    <tableColumn name="ID Cas de test (Jira)" id="9"/>
+    <tableColumn name="ID Cas de test (Jira)" id="2"/>
+    <tableColumn name="Titre  Cas de test" id="3"/>
+    <tableColumn name="Règles métier" id="4"/>
+    <tableColumn name="Priorité" id="5"/>
+    <tableColumn name="Les critères d'acceptation" id="6"/>
+    <tableColumn name="Technique de conception" id="7"/>
+    <tableColumn name="Niveau de test" id="8"/>
+    <tableColumn name="Type de test" id="9"/>
     <tableColumn name="Préconditions" id="10"/>
     <tableColumn name="Données de test" id="11"/>
     <tableColumn name="Résultat attendu" id="12"/>
@@ -1003,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
@@ -1024,50 +1024,50 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1"/>
@@ -2079,10 +2079,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2091,63 +2091,63 @@
         <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1"/>
@@ -3154,9 +3154,10 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="18.63"/>
-    <col customWidth="1" min="2" max="2" width="17.88"/>
-    <col customWidth="1" min="3" max="3" width="18.88"/>
-    <col customWidth="1" min="4" max="11" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="12.63"/>
+    <col customWidth="1" min="3" max="3" width="17.88"/>
+    <col customWidth="1" min="4" max="4" width="18.88"/>
+    <col customWidth="1" min="5" max="11" width="12.63"/>
     <col customWidth="1" min="12" max="12" width="18.25"/>
     <col customWidth="1" min="13" max="13" width="12.63"/>
     <col customWidth="1" min="14" max="14" width="15.5"/>
@@ -3164,216 +3165,216 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="8" t="s">
+      <c r="A1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="M1" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="O1" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="13" t="s">
+      <c r="P1" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="L1" s="8" t="s">
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="O1" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="P1" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="19" t="s">
+      <c r="C2" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="D2" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="E2" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="F2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="G2" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="H2" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="I2" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="K2" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="L2" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="M2" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="N2" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="O2" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="N2" s="23" t="s">
+      <c r="P2" s="16"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="O2" s="24" t="s">
+      <c r="C3" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
-      <c r="V2" s="18"/>
-      <c r="W2" s="18"/>
-      <c r="X2" s="18"/>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="E3" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="20" t="s">
+      <c r="G3" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="H3" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J3" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="G3" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="J3" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="K3" s="21"/>
+      <c r="K3" s="16"/>
       <c r="L3" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="M3" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="N3" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="O3" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="18"/>
-      <c r="R3" s="18"/>
-      <c r="S3" s="18"/>
-      <c r="T3" s="18"/>
-      <c r="U3" s="18"/>
-      <c r="V3" s="18"/>
-      <c r="W3" s="18"/>
-      <c r="X3" s="18"/>
+        <v>80</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>15</v>
-      </c>
       <c r="D4" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>93</v>
+        <v>16</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>84</v>
       </c>
       <c r="G4" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="J4" s="29" t="s">
-        <v>70</v>
-      </c>
       <c r="K4" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="N4" s="27"/>
-      <c r="O4" s="24" t="s">
-        <v>75</v>
+        <v>86</v>
+      </c>
+      <c r="L4" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="M4" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="N4" s="28"/>
+      <c r="O4" s="21" t="s">
+        <v>72</v>
       </c>
       <c r="P4" s="31"/>
       <c r="Q4" s="32"/>
@@ -3387,49 +3388,49 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>100</v>
+      <c r="D5" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>62</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="G5" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="J5" s="20" t="s">
+      <c r="K5" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="M5" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="K5" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="L5" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="M5" s="22" t="s">
-        <v>73</v>
-      </c>
       <c r="N5" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>75</v>
+        <v>96</v>
+      </c>
+      <c r="O5" s="21" t="s">
+        <v>72</v>
       </c>
       <c r="P5" s="31"/>
       <c r="Q5" s="32"/>
@@ -3443,49 +3444,49 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>106</v>
+      <c r="D6" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>62</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="G6" s="31" t="s">
-        <v>67</v>
+        <v>99</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>93</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="J6" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="K6" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="L6" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="K6" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="L6" s="23" t="s">
+      <c r="M6" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="N6" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="M6" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="N6" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>75</v>
+      <c r="O6" s="21" t="s">
+        <v>72</v>
       </c>
       <c r="P6" s="31"/>
       <c r="Q6" s="32"/>
@@ -3499,45 +3500,45 @@
     </row>
     <row r="7" ht="100.5" customHeight="1">
       <c r="A7" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>112</v>
+      <c r="D7" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>62</v>
       </c>
       <c r="F7" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="G7" s="31" t="s">
-        <v>67</v>
+      <c r="G7" s="33" t="s">
+        <v>114</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="I7" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="J7" s="20" t="s">
-        <v>85</v>
+        <v>65</v>
+      </c>
+      <c r="I7" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>78</v>
       </c>
       <c r="K7" s="31"/>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="M7" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="N7" s="27"/>
-      <c r="O7" s="24" t="s">
-        <v>75</v>
+      <c r="M7" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="N7" s="28"/>
+      <c r="O7" s="21" t="s">
+        <v>72</v>
       </c>
       <c r="P7" s="36"/>
       <c r="Q7" s="37"/>
@@ -3551,47 +3552,47 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="33" t="s">
+      <c r="D8" s="38" t="s">
         <v>117</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>62</v>
       </c>
       <c r="F8" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="G8" s="31" t="s">
-        <v>67</v>
+      <c r="G8" s="33" t="s">
+        <v>119</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="J8" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="14" t="s">
         <v>120</v>
       </c>
       <c r="K8" s="31"/>
       <c r="L8" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="M8" s="22" t="s">
-        <v>73</v>
+      <c r="M8" s="18" t="s">
+        <v>70</v>
       </c>
       <c r="N8" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="O8" s="24" t="s">
-        <v>75</v>
+      <c r="O8" s="21" t="s">
+        <v>72</v>
       </c>
       <c r="P8" s="36"/>
       <c r="Q8" s="37"/>
@@ -3605,47 +3606,47 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>123</v>
+      <c r="D9" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>62</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>67</v>
+        <v>124</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>119</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="I9" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="J9" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>125</v>
       </c>
       <c r="K9" s="31"/>
       <c r="L9" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="M9" s="22" t="s">
-        <v>73</v>
+      <c r="M9" s="18" t="s">
+        <v>70</v>
       </c>
       <c r="N9" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="O9" s="24" t="s">
-        <v>75</v>
+      <c r="O9" s="21" t="s">
+        <v>72</v>
       </c>
       <c r="P9" s="41" t="s">
         <v>128</v>
@@ -3662,13 +3663,13 @@
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="32"/>
       <c r="B10" s="42"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="44"/>
       <c r="F10" s="42"/>
-      <c r="G10" s="44"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="44"/>
-      <c r="I10" s="42"/>
+      <c r="I10" s="44"/>
       <c r="J10" s="42"/>
       <c r="K10" s="44"/>
       <c r="L10" s="42"/>
@@ -3689,12 +3690,12 @@
       <c r="A11" s="32"/>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="44"/>
       <c r="F11" s="42"/>
-      <c r="G11" s="44"/>
+      <c r="G11" s="42"/>
       <c r="H11" s="44"/>
-      <c r="I11" s="42"/>
+      <c r="I11" s="44"/>
       <c r="J11" s="42"/>
       <c r="K11" s="44"/>
       <c r="L11" s="42"/>
@@ -3715,12 +3716,12 @@
       <c r="A12" s="32"/>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="44"/>
       <c r="F12" s="42"/>
-      <c r="G12" s="44"/>
+      <c r="G12" s="42"/>
       <c r="H12" s="44"/>
-      <c r="I12" s="42"/>
+      <c r="I12" s="44"/>
       <c r="J12" s="42"/>
       <c r="K12" s="44"/>
       <c r="L12" s="42"/>
@@ -3741,12 +3742,12 @@
       <c r="A13" s="32"/>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="44"/>
       <c r="F13" s="42"/>
-      <c r="G13" s="44"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="44"/>
-      <c r="I13" s="42"/>
+      <c r="I13" s="44"/>
       <c r="J13" s="42"/>
       <c r="K13" s="44"/>
       <c r="L13" s="42"/>
@@ -3767,12 +3768,12 @@
       <c r="A14" s="32"/>
       <c r="B14" s="42"/>
       <c r="C14" s="42"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="44"/>
       <c r="F14" s="42"/>
-      <c r="G14" s="44"/>
+      <c r="G14" s="42"/>
       <c r="H14" s="44"/>
-      <c r="I14" s="42"/>
+      <c r="I14" s="44"/>
       <c r="J14" s="42"/>
       <c r="K14" s="44"/>
       <c r="L14" s="42"/>
@@ -3793,12 +3794,12 @@
       <c r="A15" s="32"/>
       <c r="B15" s="42"/>
       <c r="C15" s="42"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="44"/>
       <c r="F15" s="42"/>
-      <c r="G15" s="44"/>
+      <c r="G15" s="42"/>
       <c r="H15" s="44"/>
-      <c r="I15" s="42"/>
+      <c r="I15" s="44"/>
       <c r="J15" s="42"/>
       <c r="K15" s="44"/>
       <c r="L15" s="42"/>
@@ -3819,12 +3820,12 @@
       <c r="A16" s="32"/>
       <c r="B16" s="42"/>
       <c r="C16" s="42"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="44"/>
       <c r="F16" s="42"/>
-      <c r="G16" s="44"/>
+      <c r="G16" s="42"/>
       <c r="H16" s="44"/>
-      <c r="I16" s="42"/>
+      <c r="I16" s="44"/>
       <c r="J16" s="42"/>
       <c r="K16" s="44"/>
       <c r="L16" s="42"/>
@@ -3845,12 +3846,12 @@
       <c r="A17" s="32"/>
       <c r="B17" s="42"/>
       <c r="C17" s="42"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="44"/>
       <c r="F17" s="42"/>
-      <c r="G17" s="44"/>
+      <c r="G17" s="42"/>
       <c r="H17" s="44"/>
-      <c r="I17" s="42"/>
+      <c r="I17" s="44"/>
       <c r="J17" s="42"/>
       <c r="K17" s="44"/>
       <c r="L17" s="42"/>
@@ -3871,12 +3872,12 @@
       <c r="A18" s="32"/>
       <c r="B18" s="42"/>
       <c r="C18" s="42"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="44"/>
       <c r="F18" s="42"/>
-      <c r="G18" s="44"/>
+      <c r="G18" s="42"/>
       <c r="H18" s="44"/>
-      <c r="I18" s="42"/>
+      <c r="I18" s="44"/>
       <c r="J18" s="42"/>
       <c r="K18" s="44"/>
       <c r="L18" s="42"/>
@@ -3897,12 +3898,12 @@
       <c r="A19" s="32"/>
       <c r="B19" s="42"/>
       <c r="C19" s="42"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="44"/>
       <c r="F19" s="42"/>
-      <c r="G19" s="44"/>
+      <c r="G19" s="42"/>
       <c r="H19" s="44"/>
-      <c r="I19" s="42"/>
+      <c r="I19" s="44"/>
       <c r="J19" s="42"/>
       <c r="K19" s="44"/>
       <c r="L19" s="42"/>
@@ -3923,12 +3924,12 @@
       <c r="A20" s="32"/>
       <c r="B20" s="42"/>
       <c r="C20" s="42"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="44"/>
       <c r="F20" s="42"/>
-      <c r="G20" s="44"/>
+      <c r="G20" s="42"/>
       <c r="H20" s="44"/>
-      <c r="I20" s="42"/>
+      <c r="I20" s="44"/>
       <c r="J20" s="42"/>
       <c r="K20" s="44"/>
       <c r="L20" s="42"/>
@@ -3949,12 +3950,12 @@
       <c r="A21" s="32"/>
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="44"/>
       <c r="F21" s="42"/>
-      <c r="G21" s="44"/>
+      <c r="G21" s="42"/>
       <c r="H21" s="44"/>
-      <c r="I21" s="42"/>
+      <c r="I21" s="44"/>
       <c r="J21" s="42"/>
       <c r="K21" s="44"/>
       <c r="L21" s="42"/>
@@ -3975,12 +3976,12 @@
       <c r="A22" s="32"/>
       <c r="B22" s="42"/>
       <c r="C22" s="42"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="44"/>
       <c r="F22" s="42"/>
-      <c r="G22" s="44"/>
+      <c r="G22" s="42"/>
       <c r="H22" s="44"/>
-      <c r="I22" s="42"/>
+      <c r="I22" s="44"/>
       <c r="J22" s="42"/>
       <c r="K22" s="44"/>
       <c r="L22" s="42"/>
@@ -4001,12 +4002,12 @@
       <c r="A23" s="32"/>
       <c r="B23" s="42"/>
       <c r="C23" s="42"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="44"/>
       <c r="F23" s="42"/>
-      <c r="G23" s="44"/>
+      <c r="G23" s="42"/>
       <c r="H23" s="44"/>
-      <c r="I23" s="42"/>
+      <c r="I23" s="44"/>
       <c r="J23" s="42"/>
       <c r="K23" s="44"/>
       <c r="L23" s="42"/>
@@ -4027,12 +4028,12 @@
       <c r="A24" s="32"/>
       <c r="B24" s="42"/>
       <c r="C24" s="42"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="44"/>
       <c r="F24" s="42"/>
-      <c r="G24" s="44"/>
+      <c r="G24" s="42"/>
       <c r="H24" s="44"/>
-      <c r="I24" s="42"/>
+      <c r="I24" s="44"/>
       <c r="J24" s="42"/>
       <c r="K24" s="44"/>
       <c r="L24" s="42"/>
@@ -4053,12 +4054,12 @@
       <c r="A25" s="32"/>
       <c r="B25" s="42"/>
       <c r="C25" s="42"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="44"/>
       <c r="F25" s="42"/>
-      <c r="G25" s="44"/>
+      <c r="G25" s="42"/>
       <c r="H25" s="44"/>
-      <c r="I25" s="42"/>
+      <c r="I25" s="44"/>
       <c r="J25" s="42"/>
       <c r="K25" s="44"/>
       <c r="L25" s="42"/>
@@ -4079,12 +4080,12 @@
       <c r="A26" s="32"/>
       <c r="B26" s="42"/>
       <c r="C26" s="42"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="44"/>
       <c r="F26" s="42"/>
-      <c r="G26" s="44"/>
+      <c r="G26" s="42"/>
       <c r="H26" s="44"/>
-      <c r="I26" s="42"/>
+      <c r="I26" s="44"/>
       <c r="J26" s="42"/>
       <c r="K26" s="44"/>
       <c r="L26" s="42"/>
@@ -4105,12 +4106,12 @@
       <c r="A27" s="32"/>
       <c r="B27" s="42"/>
       <c r="C27" s="42"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="44"/>
       <c r="F27" s="42"/>
-      <c r="G27" s="44"/>
+      <c r="G27" s="42"/>
       <c r="H27" s="44"/>
-      <c r="I27" s="42"/>
+      <c r="I27" s="44"/>
       <c r="J27" s="42"/>
       <c r="K27" s="44"/>
       <c r="L27" s="42"/>
@@ -4131,12 +4132,12 @@
       <c r="A28" s="32"/>
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="42"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="44"/>
       <c r="F28" s="42"/>
-      <c r="G28" s="44"/>
+      <c r="G28" s="42"/>
       <c r="H28" s="44"/>
-      <c r="I28" s="42"/>
+      <c r="I28" s="44"/>
       <c r="J28" s="42"/>
       <c r="K28" s="44"/>
       <c r="L28" s="42"/>
@@ -4157,12 +4158,12 @@
       <c r="A29" s="32"/>
       <c r="B29" s="42"/>
       <c r="C29" s="42"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="44"/>
       <c r="F29" s="42"/>
-      <c r="G29" s="44"/>
+      <c r="G29" s="42"/>
       <c r="H29" s="44"/>
-      <c r="I29" s="42"/>
+      <c r="I29" s="44"/>
       <c r="J29" s="42"/>
       <c r="K29" s="44"/>
       <c r="L29" s="42"/>
@@ -4183,12 +4184,12 @@
       <c r="A30" s="32"/>
       <c r="B30" s="42"/>
       <c r="C30" s="42"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="42"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="44"/>
       <c r="F30" s="42"/>
-      <c r="G30" s="44"/>
+      <c r="G30" s="42"/>
       <c r="H30" s="44"/>
-      <c r="I30" s="42"/>
+      <c r="I30" s="44"/>
       <c r="J30" s="42"/>
       <c r="K30" s="44"/>
       <c r="L30" s="42"/>
@@ -4209,12 +4210,12 @@
       <c r="A31" s="32"/>
       <c r="B31" s="42"/>
       <c r="C31" s="42"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="44"/>
       <c r="F31" s="42"/>
-      <c r="G31" s="44"/>
+      <c r="G31" s="42"/>
       <c r="H31" s="44"/>
-      <c r="I31" s="42"/>
+      <c r="I31" s="44"/>
       <c r="J31" s="42"/>
       <c r="K31" s="44"/>
       <c r="L31" s="42"/>
@@ -4235,12 +4236,12 @@
       <c r="A32" s="32"/>
       <c r="B32" s="42"/>
       <c r="C32" s="42"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="44"/>
       <c r="F32" s="42"/>
-      <c r="G32" s="44"/>
+      <c r="G32" s="42"/>
       <c r="H32" s="44"/>
-      <c r="I32" s="42"/>
+      <c r="I32" s="44"/>
       <c r="J32" s="42"/>
       <c r="K32" s="44"/>
       <c r="L32" s="42"/>
@@ -4261,12 +4262,12 @@
       <c r="A33" s="32"/>
       <c r="B33" s="42"/>
       <c r="C33" s="42"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="44"/>
       <c r="F33" s="42"/>
-      <c r="G33" s="44"/>
+      <c r="G33" s="42"/>
       <c r="H33" s="44"/>
-      <c r="I33" s="42"/>
+      <c r="I33" s="44"/>
       <c r="J33" s="42"/>
       <c r="K33" s="44"/>
       <c r="L33" s="42"/>
@@ -4287,12 +4288,12 @@
       <c r="A34" s="32"/>
       <c r="B34" s="42"/>
       <c r="C34" s="42"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="44"/>
       <c r="F34" s="42"/>
-      <c r="G34" s="44"/>
+      <c r="G34" s="42"/>
       <c r="H34" s="44"/>
-      <c r="I34" s="42"/>
+      <c r="I34" s="44"/>
       <c r="J34" s="42"/>
       <c r="K34" s="44"/>
       <c r="L34" s="42"/>
@@ -4313,12 +4314,12 @@
       <c r="A35" s="32"/>
       <c r="B35" s="42"/>
       <c r="C35" s="42"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="44"/>
       <c r="F35" s="42"/>
-      <c r="G35" s="44"/>
+      <c r="G35" s="42"/>
       <c r="H35" s="44"/>
-      <c r="I35" s="42"/>
+      <c r="I35" s="44"/>
       <c r="J35" s="42"/>
       <c r="K35" s="44"/>
       <c r="L35" s="42"/>
@@ -4339,12 +4340,12 @@
       <c r="A36" s="32"/>
       <c r="B36" s="42"/>
       <c r="C36" s="42"/>
-      <c r="D36" s="44"/>
-      <c r="E36" s="42"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="44"/>
       <c r="F36" s="42"/>
-      <c r="G36" s="44"/>
+      <c r="G36" s="42"/>
       <c r="H36" s="44"/>
-      <c r="I36" s="42"/>
+      <c r="I36" s="44"/>
       <c r="J36" s="42"/>
       <c r="K36" s="44"/>
       <c r="L36" s="42"/>
@@ -4365,12 +4366,12 @@
       <c r="A37" s="32"/>
       <c r="B37" s="42"/>
       <c r="C37" s="42"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="42"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="44"/>
       <c r="F37" s="42"/>
-      <c r="G37" s="44"/>
+      <c r="G37" s="42"/>
       <c r="H37" s="44"/>
-      <c r="I37" s="42"/>
+      <c r="I37" s="44"/>
       <c r="J37" s="42"/>
       <c r="K37" s="44"/>
       <c r="L37" s="42"/>
@@ -4391,12 +4392,12 @@
       <c r="A38" s="32"/>
       <c r="B38" s="42"/>
       <c r="C38" s="42"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="44"/>
       <c r="F38" s="42"/>
-      <c r="G38" s="44"/>
+      <c r="G38" s="42"/>
       <c r="H38" s="44"/>
-      <c r="I38" s="42"/>
+      <c r="I38" s="44"/>
       <c r="J38" s="42"/>
       <c r="K38" s="44"/>
       <c r="L38" s="42"/>
@@ -4417,12 +4418,12 @@
       <c r="A39" s="32"/>
       <c r="B39" s="42"/>
       <c r="C39" s="42"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="42"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="44"/>
       <c r="F39" s="42"/>
-      <c r="G39" s="44"/>
+      <c r="G39" s="42"/>
       <c r="H39" s="44"/>
-      <c r="I39" s="42"/>
+      <c r="I39" s="44"/>
       <c r="J39" s="42"/>
       <c r="K39" s="44"/>
       <c r="L39" s="42"/>
@@ -4443,12 +4444,12 @@
       <c r="A40" s="32"/>
       <c r="B40" s="42"/>
       <c r="C40" s="42"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="42"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="44"/>
       <c r="F40" s="42"/>
-      <c r="G40" s="44"/>
+      <c r="G40" s="42"/>
       <c r="H40" s="44"/>
-      <c r="I40" s="42"/>
+      <c r="I40" s="44"/>
       <c r="J40" s="42"/>
       <c r="K40" s="44"/>
       <c r="L40" s="42"/>
@@ -4469,12 +4470,12 @@
       <c r="A41" s="32"/>
       <c r="B41" s="42"/>
       <c r="C41" s="42"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="42"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="44"/>
       <c r="F41" s="42"/>
-      <c r="G41" s="44"/>
+      <c r="G41" s="42"/>
       <c r="H41" s="44"/>
-      <c r="I41" s="42"/>
+      <c r="I41" s="44"/>
       <c r="J41" s="42"/>
       <c r="K41" s="44"/>
       <c r="L41" s="42"/>
@@ -4495,12 +4496,12 @@
       <c r="A42" s="32"/>
       <c r="B42" s="42"/>
       <c r="C42" s="42"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="44"/>
       <c r="F42" s="42"/>
-      <c r="G42" s="44"/>
+      <c r="G42" s="42"/>
       <c r="H42" s="44"/>
-      <c r="I42" s="42"/>
+      <c r="I42" s="44"/>
       <c r="J42" s="42"/>
       <c r="K42" s="44"/>
       <c r="L42" s="42"/>
@@ -4521,12 +4522,12 @@
       <c r="A43" s="32"/>
       <c r="B43" s="42"/>
       <c r="C43" s="42"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="42"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="44"/>
       <c r="F43" s="42"/>
-      <c r="G43" s="44"/>
+      <c r="G43" s="42"/>
       <c r="H43" s="44"/>
-      <c r="I43" s="42"/>
+      <c r="I43" s="44"/>
       <c r="J43" s="42"/>
       <c r="K43" s="44"/>
       <c r="L43" s="42"/>
@@ -4547,12 +4548,12 @@
       <c r="A44" s="32"/>
       <c r="B44" s="42"/>
       <c r="C44" s="42"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="42"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="44"/>
       <c r="F44" s="42"/>
-      <c r="G44" s="44"/>
+      <c r="G44" s="42"/>
       <c r="H44" s="44"/>
-      <c r="I44" s="42"/>
+      <c r="I44" s="44"/>
       <c r="J44" s="42"/>
       <c r="K44" s="44"/>
       <c r="L44" s="42"/>
@@ -4573,12 +4574,12 @@
       <c r="A45" s="32"/>
       <c r="B45" s="42"/>
       <c r="C45" s="42"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="44"/>
       <c r="F45" s="42"/>
-      <c r="G45" s="44"/>
+      <c r="G45" s="42"/>
       <c r="H45" s="44"/>
-      <c r="I45" s="42"/>
+      <c r="I45" s="44"/>
       <c r="J45" s="42"/>
       <c r="K45" s="44"/>
       <c r="L45" s="42"/>
@@ -4599,12 +4600,12 @@
       <c r="A46" s="32"/>
       <c r="B46" s="42"/>
       <c r="C46" s="42"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="42"/>
+      <c r="D46" s="42"/>
+      <c r="E46" s="44"/>
       <c r="F46" s="42"/>
-      <c r="G46" s="44"/>
+      <c r="G46" s="42"/>
       <c r="H46" s="44"/>
-      <c r="I46" s="42"/>
+      <c r="I46" s="44"/>
       <c r="J46" s="42"/>
       <c r="K46" s="44"/>
       <c r="L46" s="42"/>
@@ -4625,12 +4626,12 @@
       <c r="A47" s="32"/>
       <c r="B47" s="42"/>
       <c r="C47" s="42"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="42"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="44"/>
       <c r="F47" s="42"/>
-      <c r="G47" s="44"/>
+      <c r="G47" s="42"/>
       <c r="H47" s="44"/>
-      <c r="I47" s="42"/>
+      <c r="I47" s="44"/>
       <c r="J47" s="42"/>
       <c r="K47" s="44"/>
       <c r="L47" s="42"/>
@@ -4651,12 +4652,12 @@
       <c r="A48" s="32"/>
       <c r="B48" s="42"/>
       <c r="C48" s="42"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="42"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="44"/>
       <c r="F48" s="42"/>
-      <c r="G48" s="44"/>
+      <c r="G48" s="42"/>
       <c r="H48" s="44"/>
-      <c r="I48" s="42"/>
+      <c r="I48" s="44"/>
       <c r="J48" s="42"/>
       <c r="K48" s="44"/>
       <c r="L48" s="42"/>
@@ -4677,12 +4678,12 @@
       <c r="A49" s="32"/>
       <c r="B49" s="42"/>
       <c r="C49" s="42"/>
-      <c r="D49" s="44"/>
-      <c r="E49" s="42"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="44"/>
       <c r="F49" s="42"/>
-      <c r="G49" s="44"/>
+      <c r="G49" s="42"/>
       <c r="H49" s="44"/>
-      <c r="I49" s="42"/>
+      <c r="I49" s="44"/>
       <c r="J49" s="42"/>
       <c r="K49" s="44"/>
       <c r="L49" s="42"/>
@@ -4703,12 +4704,12 @@
       <c r="A50" s="32"/>
       <c r="B50" s="42"/>
       <c r="C50" s="42"/>
-      <c r="D50" s="44"/>
-      <c r="E50" s="42"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="44"/>
       <c r="F50" s="42"/>
-      <c r="G50" s="44"/>
+      <c r="G50" s="42"/>
       <c r="H50" s="44"/>
-      <c r="I50" s="42"/>
+      <c r="I50" s="44"/>
       <c r="J50" s="42"/>
       <c r="K50" s="44"/>
       <c r="L50" s="42"/>
@@ -4729,12 +4730,12 @@
       <c r="A51" s="32"/>
       <c r="B51" s="42"/>
       <c r="C51" s="42"/>
-      <c r="D51" s="44"/>
-      <c r="E51" s="42"/>
+      <c r="D51" s="42"/>
+      <c r="E51" s="44"/>
       <c r="F51" s="42"/>
-      <c r="G51" s="44"/>
+      <c r="G51" s="42"/>
       <c r="H51" s="44"/>
-      <c r="I51" s="42"/>
+      <c r="I51" s="44"/>
       <c r="J51" s="42"/>
       <c r="K51" s="44"/>
       <c r="L51" s="42"/>
@@ -4755,12 +4756,12 @@
       <c r="A52" s="32"/>
       <c r="B52" s="42"/>
       <c r="C52" s="42"/>
-      <c r="D52" s="44"/>
-      <c r="E52" s="42"/>
+      <c r="D52" s="42"/>
+      <c r="E52" s="44"/>
       <c r="F52" s="42"/>
-      <c r="G52" s="44"/>
+      <c r="G52" s="42"/>
       <c r="H52" s="44"/>
-      <c r="I52" s="42"/>
+      <c r="I52" s="44"/>
       <c r="J52" s="42"/>
       <c r="K52" s="44"/>
       <c r="L52" s="42"/>
@@ -4781,12 +4782,12 @@
       <c r="A53" s="32"/>
       <c r="B53" s="42"/>
       <c r="C53" s="42"/>
-      <c r="D53" s="44"/>
-      <c r="E53" s="42"/>
+      <c r="D53" s="42"/>
+      <c r="E53" s="44"/>
       <c r="F53" s="42"/>
-      <c r="G53" s="44"/>
+      <c r="G53" s="42"/>
       <c r="H53" s="44"/>
-      <c r="I53" s="42"/>
+      <c r="I53" s="44"/>
       <c r="J53" s="42"/>
       <c r="K53" s="44"/>
       <c r="L53" s="42"/>
@@ -4807,12 +4808,12 @@
       <c r="A54" s="32"/>
       <c r="B54" s="42"/>
       <c r="C54" s="42"/>
-      <c r="D54" s="44"/>
-      <c r="E54" s="42"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="44"/>
       <c r="F54" s="42"/>
-      <c r="G54" s="44"/>
+      <c r="G54" s="42"/>
       <c r="H54" s="44"/>
-      <c r="I54" s="42"/>
+      <c r="I54" s="44"/>
       <c r="J54" s="42"/>
       <c r="K54" s="44"/>
       <c r="L54" s="42"/>
@@ -4833,12 +4834,12 @@
       <c r="A55" s="32"/>
       <c r="B55" s="42"/>
       <c r="C55" s="42"/>
-      <c r="D55" s="44"/>
-      <c r="E55" s="42"/>
+      <c r="D55" s="42"/>
+      <c r="E55" s="44"/>
       <c r="F55" s="42"/>
-      <c r="G55" s="44"/>
+      <c r="G55" s="42"/>
       <c r="H55" s="44"/>
-      <c r="I55" s="42"/>
+      <c r="I55" s="44"/>
       <c r="J55" s="42"/>
       <c r="K55" s="44"/>
       <c r="L55" s="42"/>
@@ -4859,12 +4860,12 @@
       <c r="A56" s="32"/>
       <c r="B56" s="42"/>
       <c r="C56" s="42"/>
-      <c r="D56" s="44"/>
-      <c r="E56" s="42"/>
+      <c r="D56" s="42"/>
+      <c r="E56" s="44"/>
       <c r="F56" s="42"/>
-      <c r="G56" s="44"/>
+      <c r="G56" s="42"/>
       <c r="H56" s="44"/>
-      <c r="I56" s="42"/>
+      <c r="I56" s="44"/>
       <c r="J56" s="42"/>
       <c r="K56" s="44"/>
       <c r="L56" s="42"/>
@@ -4885,12 +4886,12 @@
       <c r="A57" s="32"/>
       <c r="B57" s="42"/>
       <c r="C57" s="42"/>
-      <c r="D57" s="44"/>
-      <c r="E57" s="42"/>
+      <c r="D57" s="42"/>
+      <c r="E57" s="44"/>
       <c r="F57" s="42"/>
-      <c r="G57" s="44"/>
+      <c r="G57" s="42"/>
       <c r="H57" s="44"/>
-      <c r="I57" s="42"/>
+      <c r="I57" s="44"/>
       <c r="J57" s="42"/>
       <c r="K57" s="44"/>
       <c r="L57" s="42"/>
@@ -4911,12 +4912,12 @@
       <c r="A58" s="32"/>
       <c r="B58" s="42"/>
       <c r="C58" s="42"/>
-      <c r="D58" s="44"/>
-      <c r="E58" s="42"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="44"/>
       <c r="F58" s="42"/>
-      <c r="G58" s="44"/>
+      <c r="G58" s="42"/>
       <c r="H58" s="44"/>
-      <c r="I58" s="42"/>
+      <c r="I58" s="44"/>
       <c r="J58" s="42"/>
       <c r="K58" s="44"/>
       <c r="L58" s="42"/>
@@ -4937,12 +4938,12 @@
       <c r="A59" s="32"/>
       <c r="B59" s="42"/>
       <c r="C59" s="42"/>
-      <c r="D59" s="44"/>
-      <c r="E59" s="42"/>
+      <c r="D59" s="42"/>
+      <c r="E59" s="44"/>
       <c r="F59" s="42"/>
-      <c r="G59" s="44"/>
+      <c r="G59" s="42"/>
       <c r="H59" s="44"/>
-      <c r="I59" s="42"/>
+      <c r="I59" s="44"/>
       <c r="J59" s="42"/>
       <c r="K59" s="44"/>
       <c r="L59" s="42"/>
@@ -4963,12 +4964,12 @@
       <c r="A60" s="32"/>
       <c r="B60" s="42"/>
       <c r="C60" s="42"/>
-      <c r="D60" s="44"/>
-      <c r="E60" s="42"/>
+      <c r="D60" s="42"/>
+      <c r="E60" s="44"/>
       <c r="F60" s="42"/>
-      <c r="G60" s="44"/>
+      <c r="G60" s="42"/>
       <c r="H60" s="44"/>
-      <c r="I60" s="42"/>
+      <c r="I60" s="44"/>
       <c r="J60" s="42"/>
       <c r="K60" s="44"/>
       <c r="L60" s="42"/>
@@ -4989,12 +4990,12 @@
       <c r="A61" s="32"/>
       <c r="B61" s="42"/>
       <c r="C61" s="42"/>
-      <c r="D61" s="44"/>
-      <c r="E61" s="42"/>
+      <c r="D61" s="42"/>
+      <c r="E61" s="44"/>
       <c r="F61" s="42"/>
-      <c r="G61" s="44"/>
+      <c r="G61" s="42"/>
       <c r="H61" s="44"/>
-      <c r="I61" s="42"/>
+      <c r="I61" s="44"/>
       <c r="J61" s="42"/>
       <c r="K61" s="44"/>
       <c r="L61" s="42"/>
@@ -5015,12 +5016,12 @@
       <c r="A62" s="32"/>
       <c r="B62" s="42"/>
       <c r="C62" s="42"/>
-      <c r="D62" s="44"/>
-      <c r="E62" s="42"/>
+      <c r="D62" s="42"/>
+      <c r="E62" s="44"/>
       <c r="F62" s="42"/>
-      <c r="G62" s="44"/>
+      <c r="G62" s="42"/>
       <c r="H62" s="44"/>
-      <c r="I62" s="42"/>
+      <c r="I62" s="44"/>
       <c r="J62" s="42"/>
       <c r="K62" s="44"/>
       <c r="L62" s="42"/>
@@ -5041,12 +5042,12 @@
       <c r="A63" s="32"/>
       <c r="B63" s="42"/>
       <c r="C63" s="42"/>
-      <c r="D63" s="44"/>
-      <c r="E63" s="42"/>
+      <c r="D63" s="42"/>
+      <c r="E63" s="44"/>
       <c r="F63" s="42"/>
-      <c r="G63" s="44"/>
+      <c r="G63" s="42"/>
       <c r="H63" s="44"/>
-      <c r="I63" s="42"/>
+      <c r="I63" s="44"/>
       <c r="J63" s="42"/>
       <c r="K63" s="44"/>
       <c r="L63" s="42"/>
@@ -5067,12 +5068,12 @@
       <c r="A64" s="32"/>
       <c r="B64" s="42"/>
       <c r="C64" s="42"/>
-      <c r="D64" s="44"/>
-      <c r="E64" s="42"/>
+      <c r="D64" s="42"/>
+      <c r="E64" s="44"/>
       <c r="F64" s="42"/>
-      <c r="G64" s="44"/>
+      <c r="G64" s="42"/>
       <c r="H64" s="44"/>
-      <c r="I64" s="42"/>
+      <c r="I64" s="44"/>
       <c r="J64" s="42"/>
       <c r="K64" s="44"/>
       <c r="L64" s="42"/>
@@ -5093,12 +5094,12 @@
       <c r="A65" s="32"/>
       <c r="B65" s="42"/>
       <c r="C65" s="42"/>
-      <c r="D65" s="44"/>
-      <c r="E65" s="42"/>
+      <c r="D65" s="42"/>
+      <c r="E65" s="44"/>
       <c r="F65" s="42"/>
-      <c r="G65" s="44"/>
+      <c r="G65" s="42"/>
       <c r="H65" s="44"/>
-      <c r="I65" s="42"/>
+      <c r="I65" s="44"/>
       <c r="J65" s="42"/>
       <c r="K65" s="44"/>
       <c r="L65" s="42"/>
@@ -5119,12 +5120,12 @@
       <c r="A66" s="32"/>
       <c r="B66" s="42"/>
       <c r="C66" s="42"/>
-      <c r="D66" s="44"/>
-      <c r="E66" s="42"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="44"/>
       <c r="F66" s="42"/>
-      <c r="G66" s="44"/>
+      <c r="G66" s="42"/>
       <c r="H66" s="44"/>
-      <c r="I66" s="42"/>
+      <c r="I66" s="44"/>
       <c r="J66" s="42"/>
       <c r="K66" s="44"/>
       <c r="L66" s="42"/>
@@ -5145,12 +5146,12 @@
       <c r="A67" s="32"/>
       <c r="B67" s="42"/>
       <c r="C67" s="42"/>
-      <c r="D67" s="44"/>
-      <c r="E67" s="42"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="44"/>
       <c r="F67" s="42"/>
-      <c r="G67" s="44"/>
+      <c r="G67" s="42"/>
       <c r="H67" s="44"/>
-      <c r="I67" s="42"/>
+      <c r="I67" s="44"/>
       <c r="J67" s="42"/>
       <c r="K67" s="44"/>
       <c r="L67" s="42"/>
@@ -5171,12 +5172,12 @@
       <c r="A68" s="32"/>
       <c r="B68" s="42"/>
       <c r="C68" s="42"/>
-      <c r="D68" s="44"/>
-      <c r="E68" s="42"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="44"/>
       <c r="F68" s="42"/>
-      <c r="G68" s="44"/>
+      <c r="G68" s="42"/>
       <c r="H68" s="44"/>
-      <c r="I68" s="42"/>
+      <c r="I68" s="44"/>
       <c r="J68" s="42"/>
       <c r="K68" s="44"/>
       <c r="L68" s="42"/>
@@ -5197,12 +5198,12 @@
       <c r="A69" s="32"/>
       <c r="B69" s="42"/>
       <c r="C69" s="42"/>
-      <c r="D69" s="44"/>
-      <c r="E69" s="42"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="44"/>
       <c r="F69" s="42"/>
-      <c r="G69" s="44"/>
+      <c r="G69" s="42"/>
       <c r="H69" s="44"/>
-      <c r="I69" s="42"/>
+      <c r="I69" s="44"/>
       <c r="J69" s="42"/>
       <c r="K69" s="44"/>
       <c r="L69" s="42"/>
@@ -5223,12 +5224,12 @@
       <c r="A70" s="32"/>
       <c r="B70" s="42"/>
       <c r="C70" s="42"/>
-      <c r="D70" s="44"/>
-      <c r="E70" s="42"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="44"/>
       <c r="F70" s="42"/>
-      <c r="G70" s="44"/>
+      <c r="G70" s="42"/>
       <c r="H70" s="44"/>
-      <c r="I70" s="42"/>
+      <c r="I70" s="44"/>
       <c r="J70" s="42"/>
       <c r="K70" s="44"/>
       <c r="L70" s="42"/>
@@ -5249,12 +5250,12 @@
       <c r="A71" s="32"/>
       <c r="B71" s="42"/>
       <c r="C71" s="42"/>
-      <c r="D71" s="44"/>
-      <c r="E71" s="42"/>
+      <c r="D71" s="42"/>
+      <c r="E71" s="44"/>
       <c r="F71" s="42"/>
-      <c r="G71" s="44"/>
+      <c r="G71" s="42"/>
       <c r="H71" s="44"/>
-      <c r="I71" s="42"/>
+      <c r="I71" s="44"/>
       <c r="J71" s="42"/>
       <c r="K71" s="44"/>
       <c r="L71" s="42"/>
@@ -5275,12 +5276,12 @@
       <c r="A72" s="32"/>
       <c r="B72" s="42"/>
       <c r="C72" s="42"/>
-      <c r="D72" s="44"/>
-      <c r="E72" s="42"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="44"/>
       <c r="F72" s="42"/>
-      <c r="G72" s="44"/>
+      <c r="G72" s="42"/>
       <c r="H72" s="44"/>
-      <c r="I72" s="42"/>
+      <c r="I72" s="44"/>
       <c r="J72" s="42"/>
       <c r="K72" s="44"/>
       <c r="L72" s="42"/>
@@ -5301,12 +5302,12 @@
       <c r="A73" s="32"/>
       <c r="B73" s="42"/>
       <c r="C73" s="42"/>
-      <c r="D73" s="44"/>
-      <c r="E73" s="42"/>
+      <c r="D73" s="42"/>
+      <c r="E73" s="44"/>
       <c r="F73" s="42"/>
-      <c r="G73" s="44"/>
+      <c r="G73" s="42"/>
       <c r="H73" s="44"/>
-      <c r="I73" s="42"/>
+      <c r="I73" s="44"/>
       <c r="J73" s="42"/>
       <c r="K73" s="44"/>
       <c r="L73" s="42"/>
@@ -5327,12 +5328,12 @@
       <c r="A74" s="32"/>
       <c r="B74" s="42"/>
       <c r="C74" s="42"/>
-      <c r="D74" s="44"/>
-      <c r="E74" s="42"/>
+      <c r="D74" s="42"/>
+      <c r="E74" s="44"/>
       <c r="F74" s="42"/>
-      <c r="G74" s="44"/>
+      <c r="G74" s="42"/>
       <c r="H74" s="44"/>
-      <c r="I74" s="42"/>
+      <c r="I74" s="44"/>
       <c r="J74" s="42"/>
       <c r="K74" s="44"/>
       <c r="L74" s="42"/>
@@ -5353,12 +5354,12 @@
       <c r="A75" s="32"/>
       <c r="B75" s="42"/>
       <c r="C75" s="42"/>
-      <c r="D75" s="44"/>
-      <c r="E75" s="42"/>
+      <c r="D75" s="42"/>
+      <c r="E75" s="44"/>
       <c r="F75" s="42"/>
-      <c r="G75" s="44"/>
+      <c r="G75" s="42"/>
       <c r="H75" s="44"/>
-      <c r="I75" s="42"/>
+      <c r="I75" s="44"/>
       <c r="J75" s="42"/>
       <c r="K75" s="44"/>
       <c r="L75" s="42"/>
@@ -5379,12 +5380,12 @@
       <c r="A76" s="32"/>
       <c r="B76" s="42"/>
       <c r="C76" s="42"/>
-      <c r="D76" s="44"/>
-      <c r="E76" s="42"/>
+      <c r="D76" s="42"/>
+      <c r="E76" s="44"/>
       <c r="F76" s="42"/>
-      <c r="G76" s="44"/>
+      <c r="G76" s="42"/>
       <c r="H76" s="44"/>
-      <c r="I76" s="42"/>
+      <c r="I76" s="44"/>
       <c r="J76" s="42"/>
       <c r="K76" s="44"/>
       <c r="L76" s="42"/>
@@ -5405,12 +5406,12 @@
       <c r="A77" s="32"/>
       <c r="B77" s="42"/>
       <c r="C77" s="42"/>
-      <c r="D77" s="44"/>
-      <c r="E77" s="42"/>
+      <c r="D77" s="42"/>
+      <c r="E77" s="44"/>
       <c r="F77" s="42"/>
-      <c r="G77" s="44"/>
+      <c r="G77" s="42"/>
       <c r="H77" s="44"/>
-      <c r="I77" s="42"/>
+      <c r="I77" s="44"/>
       <c r="J77" s="42"/>
       <c r="K77" s="44"/>
       <c r="L77" s="42"/>
@@ -5431,12 +5432,12 @@
       <c r="A78" s="32"/>
       <c r="B78" s="42"/>
       <c r="C78" s="42"/>
-      <c r="D78" s="44"/>
-      <c r="E78" s="42"/>
+      <c r="D78" s="42"/>
+      <c r="E78" s="44"/>
       <c r="F78" s="42"/>
-      <c r="G78" s="44"/>
+      <c r="G78" s="42"/>
       <c r="H78" s="44"/>
-      <c r="I78" s="42"/>
+      <c r="I78" s="44"/>
       <c r="J78" s="42"/>
       <c r="K78" s="44"/>
       <c r="L78" s="42"/>
@@ -5457,12 +5458,12 @@
       <c r="A79" s="32"/>
       <c r="B79" s="42"/>
       <c r="C79" s="42"/>
-      <c r="D79" s="44"/>
-      <c r="E79" s="42"/>
+      <c r="D79" s="42"/>
+      <c r="E79" s="44"/>
       <c r="F79" s="42"/>
-      <c r="G79" s="44"/>
+      <c r="G79" s="42"/>
       <c r="H79" s="44"/>
-      <c r="I79" s="42"/>
+      <c r="I79" s="44"/>
       <c r="J79" s="42"/>
       <c r="K79" s="44"/>
       <c r="L79" s="42"/>
@@ -5483,12 +5484,12 @@
       <c r="A80" s="32"/>
       <c r="B80" s="42"/>
       <c r="C80" s="42"/>
-      <c r="D80" s="44"/>
-      <c r="E80" s="42"/>
+      <c r="D80" s="42"/>
+      <c r="E80" s="44"/>
       <c r="F80" s="42"/>
-      <c r="G80" s="44"/>
+      <c r="G80" s="42"/>
       <c r="H80" s="44"/>
-      <c r="I80" s="42"/>
+      <c r="I80" s="44"/>
       <c r="J80" s="42"/>
       <c r="K80" s="44"/>
       <c r="L80" s="42"/>
@@ -5509,12 +5510,12 @@
       <c r="A81" s="32"/>
       <c r="B81" s="42"/>
       <c r="C81" s="42"/>
-      <c r="D81" s="44"/>
-      <c r="E81" s="42"/>
+      <c r="D81" s="42"/>
+      <c r="E81" s="44"/>
       <c r="F81" s="42"/>
-      <c r="G81" s="44"/>
+      <c r="G81" s="42"/>
       <c r="H81" s="44"/>
-      <c r="I81" s="42"/>
+      <c r="I81" s="44"/>
       <c r="J81" s="42"/>
       <c r="K81" s="44"/>
       <c r="L81" s="42"/>
@@ -5535,12 +5536,12 @@
       <c r="A82" s="32"/>
       <c r="B82" s="42"/>
       <c r="C82" s="42"/>
-      <c r="D82" s="44"/>
-      <c r="E82" s="42"/>
+      <c r="D82" s="42"/>
+      <c r="E82" s="44"/>
       <c r="F82" s="42"/>
-      <c r="G82" s="44"/>
+      <c r="G82" s="42"/>
       <c r="H82" s="44"/>
-      <c r="I82" s="42"/>
+      <c r="I82" s="44"/>
       <c r="J82" s="42"/>
       <c r="K82" s="44"/>
       <c r="L82" s="42"/>
@@ -5561,12 +5562,12 @@
       <c r="A83" s="32"/>
       <c r="B83" s="42"/>
       <c r="C83" s="42"/>
-      <c r="D83" s="44"/>
-      <c r="E83" s="42"/>
+      <c r="D83" s="42"/>
+      <c r="E83" s="44"/>
       <c r="F83" s="42"/>
-      <c r="G83" s="44"/>
+      <c r="G83" s="42"/>
       <c r="H83" s="44"/>
-      <c r="I83" s="42"/>
+      <c r="I83" s="44"/>
       <c r="J83" s="42"/>
       <c r="K83" s="44"/>
       <c r="L83" s="42"/>
@@ -5587,12 +5588,12 @@
       <c r="A84" s="32"/>
       <c r="B84" s="42"/>
       <c r="C84" s="42"/>
-      <c r="D84" s="44"/>
-      <c r="E84" s="42"/>
+      <c r="D84" s="42"/>
+      <c r="E84" s="44"/>
       <c r="F84" s="42"/>
-      <c r="G84" s="44"/>
+      <c r="G84" s="42"/>
       <c r="H84" s="44"/>
-      <c r="I84" s="42"/>
+      <c r="I84" s="44"/>
       <c r="J84" s="42"/>
       <c r="K84" s="44"/>
       <c r="L84" s="42"/>
@@ -5613,12 +5614,12 @@
       <c r="A85" s="32"/>
       <c r="B85" s="42"/>
       <c r="C85" s="42"/>
-      <c r="D85" s="44"/>
-      <c r="E85" s="42"/>
+      <c r="D85" s="42"/>
+      <c r="E85" s="44"/>
       <c r="F85" s="42"/>
-      <c r="G85" s="44"/>
+      <c r="G85" s="42"/>
       <c r="H85" s="44"/>
-      <c r="I85" s="42"/>
+      <c r="I85" s="44"/>
       <c r="J85" s="42"/>
       <c r="K85" s="44"/>
       <c r="L85" s="42"/>
@@ -5639,12 +5640,12 @@
       <c r="A86" s="32"/>
       <c r="B86" s="42"/>
       <c r="C86" s="42"/>
-      <c r="D86" s="44"/>
-      <c r="E86" s="42"/>
+      <c r="D86" s="42"/>
+      <c r="E86" s="44"/>
       <c r="F86" s="42"/>
-      <c r="G86" s="44"/>
+      <c r="G86" s="42"/>
       <c r="H86" s="44"/>
-      <c r="I86" s="42"/>
+      <c r="I86" s="44"/>
       <c r="J86" s="42"/>
       <c r="K86" s="44"/>
       <c r="L86" s="42"/>
@@ -5665,12 +5666,12 @@
       <c r="A87" s="32"/>
       <c r="B87" s="42"/>
       <c r="C87" s="42"/>
-      <c r="D87" s="44"/>
-      <c r="E87" s="42"/>
+      <c r="D87" s="42"/>
+      <c r="E87" s="44"/>
       <c r="F87" s="42"/>
-      <c r="G87" s="44"/>
+      <c r="G87" s="42"/>
       <c r="H87" s="44"/>
-      <c r="I87" s="42"/>
+      <c r="I87" s="44"/>
       <c r="J87" s="42"/>
       <c r="K87" s="44"/>
       <c r="L87" s="42"/>
@@ -5691,12 +5692,12 @@
       <c r="A88" s="32"/>
       <c r="B88" s="42"/>
       <c r="C88" s="42"/>
-      <c r="D88" s="44"/>
-      <c r="E88" s="42"/>
+      <c r="D88" s="42"/>
+      <c r="E88" s="44"/>
       <c r="F88" s="42"/>
-      <c r="G88" s="44"/>
+      <c r="G88" s="42"/>
       <c r="H88" s="44"/>
-      <c r="I88" s="42"/>
+      <c r="I88" s="44"/>
       <c r="J88" s="42"/>
       <c r="K88" s="44"/>
       <c r="L88" s="42"/>
@@ -5717,12 +5718,12 @@
       <c r="A89" s="32"/>
       <c r="B89" s="42"/>
       <c r="C89" s="42"/>
-      <c r="D89" s="44"/>
-      <c r="E89" s="42"/>
+      <c r="D89" s="42"/>
+      <c r="E89" s="44"/>
       <c r="F89" s="42"/>
-      <c r="G89" s="44"/>
+      <c r="G89" s="42"/>
       <c r="H89" s="44"/>
-      <c r="I89" s="42"/>
+      <c r="I89" s="44"/>
       <c r="J89" s="42"/>
       <c r="K89" s="44"/>
       <c r="L89" s="42"/>
@@ -5743,12 +5744,12 @@
       <c r="A90" s="32"/>
       <c r="B90" s="42"/>
       <c r="C90" s="42"/>
-      <c r="D90" s="44"/>
-      <c r="E90" s="42"/>
+      <c r="D90" s="42"/>
+      <c r="E90" s="44"/>
       <c r="F90" s="42"/>
-      <c r="G90" s="44"/>
+      <c r="G90" s="42"/>
       <c r="H90" s="44"/>
-      <c r="I90" s="42"/>
+      <c r="I90" s="44"/>
       <c r="J90" s="42"/>
       <c r="K90" s="44"/>
       <c r="L90" s="42"/>
@@ -5769,12 +5770,12 @@
       <c r="A91" s="32"/>
       <c r="B91" s="42"/>
       <c r="C91" s="42"/>
-      <c r="D91" s="44"/>
-      <c r="E91" s="42"/>
+      <c r="D91" s="42"/>
+      <c r="E91" s="44"/>
       <c r="F91" s="42"/>
-      <c r="G91" s="44"/>
+      <c r="G91" s="42"/>
       <c r="H91" s="44"/>
-      <c r="I91" s="42"/>
+      <c r="I91" s="44"/>
       <c r="J91" s="42"/>
       <c r="K91" s="44"/>
       <c r="L91" s="42"/>
@@ -5795,12 +5796,12 @@
       <c r="A92" s="32"/>
       <c r="B92" s="42"/>
       <c r="C92" s="42"/>
-      <c r="D92" s="44"/>
-      <c r="E92" s="42"/>
+      <c r="D92" s="42"/>
+      <c r="E92" s="44"/>
       <c r="F92" s="42"/>
-      <c r="G92" s="44"/>
+      <c r="G92" s="42"/>
       <c r="H92" s="44"/>
-      <c r="I92" s="42"/>
+      <c r="I92" s="44"/>
       <c r="J92" s="42"/>
       <c r="K92" s="44"/>
       <c r="L92" s="42"/>
@@ -5821,12 +5822,12 @@
       <c r="A93" s="32"/>
       <c r="B93" s="42"/>
       <c r="C93" s="42"/>
-      <c r="D93" s="44"/>
-      <c r="E93" s="42"/>
+      <c r="D93" s="42"/>
+      <c r="E93" s="44"/>
       <c r="F93" s="42"/>
-      <c r="G93" s="44"/>
+      <c r="G93" s="42"/>
       <c r="H93" s="44"/>
-      <c r="I93" s="42"/>
+      <c r="I93" s="44"/>
       <c r="J93" s="42"/>
       <c r="K93" s="44"/>
       <c r="L93" s="42"/>
@@ -5847,12 +5848,12 @@
       <c r="A94" s="32"/>
       <c r="B94" s="42"/>
       <c r="C94" s="42"/>
-      <c r="D94" s="44"/>
-      <c r="E94" s="42"/>
+      <c r="D94" s="42"/>
+      <c r="E94" s="44"/>
       <c r="F94" s="42"/>
-      <c r="G94" s="44"/>
+      <c r="G94" s="42"/>
       <c r="H94" s="44"/>
-      <c r="I94" s="42"/>
+      <c r="I94" s="44"/>
       <c r="J94" s="42"/>
       <c r="K94" s="44"/>
       <c r="L94" s="42"/>
@@ -5873,12 +5874,12 @@
       <c r="A95" s="32"/>
       <c r="B95" s="42"/>
       <c r="C95" s="42"/>
-      <c r="D95" s="44"/>
-      <c r="E95" s="42"/>
+      <c r="D95" s="42"/>
+      <c r="E95" s="44"/>
       <c r="F95" s="42"/>
-      <c r="G95" s="44"/>
+      <c r="G95" s="42"/>
       <c r="H95" s="44"/>
-      <c r="I95" s="42"/>
+      <c r="I95" s="44"/>
       <c r="J95" s="42"/>
       <c r="K95" s="44"/>
       <c r="L95" s="42"/>
@@ -5899,12 +5900,12 @@
       <c r="A96" s="32"/>
       <c r="B96" s="42"/>
       <c r="C96" s="42"/>
-      <c r="D96" s="44"/>
-      <c r="E96" s="42"/>
+      <c r="D96" s="42"/>
+      <c r="E96" s="44"/>
       <c r="F96" s="42"/>
-      <c r="G96" s="44"/>
+      <c r="G96" s="42"/>
       <c r="H96" s="44"/>
-      <c r="I96" s="42"/>
+      <c r="I96" s="44"/>
       <c r="J96" s="42"/>
       <c r="K96" s="44"/>
       <c r="L96" s="42"/>
@@ -5925,12 +5926,12 @@
       <c r="A97" s="32"/>
       <c r="B97" s="42"/>
       <c r="C97" s="42"/>
-      <c r="D97" s="44"/>
-      <c r="E97" s="42"/>
+      <c r="D97" s="42"/>
+      <c r="E97" s="44"/>
       <c r="F97" s="42"/>
-      <c r="G97" s="44"/>
+      <c r="G97" s="42"/>
       <c r="H97" s="44"/>
-      <c r="I97" s="42"/>
+      <c r="I97" s="44"/>
       <c r="J97" s="42"/>
       <c r="K97" s="44"/>
       <c r="L97" s="42"/>
@@ -5951,12 +5952,12 @@
       <c r="A98" s="32"/>
       <c r="B98" s="42"/>
       <c r="C98" s="42"/>
-      <c r="D98" s="44"/>
-      <c r="E98" s="42"/>
+      <c r="D98" s="42"/>
+      <c r="E98" s="44"/>
       <c r="F98" s="42"/>
-      <c r="G98" s="44"/>
+      <c r="G98" s="42"/>
       <c r="H98" s="44"/>
-      <c r="I98" s="42"/>
+      <c r="I98" s="44"/>
       <c r="J98" s="42"/>
       <c r="K98" s="44"/>
       <c r="L98" s="42"/>
@@ -5977,12 +5978,12 @@
       <c r="A99" s="32"/>
       <c r="B99" s="42"/>
       <c r="C99" s="42"/>
-      <c r="D99" s="44"/>
-      <c r="E99" s="42"/>
+      <c r="D99" s="42"/>
+      <c r="E99" s="44"/>
       <c r="F99" s="42"/>
-      <c r="G99" s="44"/>
+      <c r="G99" s="42"/>
       <c r="H99" s="44"/>
-      <c r="I99" s="42"/>
+      <c r="I99" s="44"/>
       <c r="J99" s="42"/>
       <c r="K99" s="44"/>
       <c r="L99" s="42"/>
@@ -6003,12 +6004,12 @@
       <c r="A100" s="32"/>
       <c r="B100" s="42"/>
       <c r="C100" s="42"/>
-      <c r="D100" s="44"/>
-      <c r="E100" s="42"/>
+      <c r="D100" s="42"/>
+      <c r="E100" s="44"/>
       <c r="F100" s="42"/>
-      <c r="G100" s="44"/>
+      <c r="G100" s="42"/>
       <c r="H100" s="44"/>
-      <c r="I100" s="42"/>
+      <c r="I100" s="44"/>
       <c r="J100" s="42"/>
       <c r="K100" s="44"/>
       <c r="L100" s="42"/>
@@ -6029,12 +6030,12 @@
       <c r="A101" s="32"/>
       <c r="B101" s="42"/>
       <c r="C101" s="42"/>
-      <c r="D101" s="44"/>
-      <c r="E101" s="42"/>
+      <c r="D101" s="42"/>
+      <c r="E101" s="44"/>
       <c r="F101" s="42"/>
-      <c r="G101" s="44"/>
+      <c r="G101" s="42"/>
       <c r="H101" s="44"/>
-      <c r="I101" s="42"/>
+      <c r="I101" s="44"/>
       <c r="J101" s="42"/>
       <c r="K101" s="44"/>
       <c r="L101" s="42"/>
@@ -6055,12 +6056,12 @@
       <c r="A102" s="32"/>
       <c r="B102" s="42"/>
       <c r="C102" s="42"/>
-      <c r="D102" s="44"/>
-      <c r="E102" s="42"/>
+      <c r="D102" s="42"/>
+      <c r="E102" s="44"/>
       <c r="F102" s="42"/>
-      <c r="G102" s="44"/>
+      <c r="G102" s="42"/>
       <c r="H102" s="44"/>
-      <c r="I102" s="42"/>
+      <c r="I102" s="44"/>
       <c r="J102" s="42"/>
       <c r="K102" s="44"/>
       <c r="L102" s="42"/>
@@ -6081,12 +6082,12 @@
       <c r="A103" s="32"/>
       <c r="B103" s="42"/>
       <c r="C103" s="42"/>
-      <c r="D103" s="44"/>
-      <c r="E103" s="42"/>
+      <c r="D103" s="42"/>
+      <c r="E103" s="44"/>
       <c r="F103" s="42"/>
-      <c r="G103" s="44"/>
+      <c r="G103" s="42"/>
       <c r="H103" s="44"/>
-      <c r="I103" s="42"/>
+      <c r="I103" s="44"/>
       <c r="J103" s="42"/>
       <c r="K103" s="44"/>
       <c r="L103" s="42"/>
@@ -6107,12 +6108,12 @@
       <c r="A104" s="32"/>
       <c r="B104" s="42"/>
       <c r="C104" s="42"/>
-      <c r="D104" s="44"/>
-      <c r="E104" s="42"/>
+      <c r="D104" s="42"/>
+      <c r="E104" s="44"/>
       <c r="F104" s="42"/>
-      <c r="G104" s="44"/>
+      <c r="G104" s="42"/>
       <c r="H104" s="44"/>
-      <c r="I104" s="42"/>
+      <c r="I104" s="44"/>
       <c r="J104" s="42"/>
       <c r="K104" s="44"/>
       <c r="L104" s="42"/>
@@ -6133,12 +6134,12 @@
       <c r="A105" s="32"/>
       <c r="B105" s="42"/>
       <c r="C105" s="42"/>
-      <c r="D105" s="44"/>
-      <c r="E105" s="42"/>
+      <c r="D105" s="42"/>
+      <c r="E105" s="44"/>
       <c r="F105" s="42"/>
-      <c r="G105" s="44"/>
+      <c r="G105" s="42"/>
       <c r="H105" s="44"/>
-      <c r="I105" s="42"/>
+      <c r="I105" s="44"/>
       <c r="J105" s="42"/>
       <c r="K105" s="44"/>
       <c r="L105" s="42"/>
@@ -6159,12 +6160,12 @@
       <c r="A106" s="32"/>
       <c r="B106" s="42"/>
       <c r="C106" s="42"/>
-      <c r="D106" s="44"/>
-      <c r="E106" s="42"/>
+      <c r="D106" s="42"/>
+      <c r="E106" s="44"/>
       <c r="F106" s="42"/>
-      <c r="G106" s="44"/>
+      <c r="G106" s="42"/>
       <c r="H106" s="44"/>
-      <c r="I106" s="42"/>
+      <c r="I106" s="44"/>
       <c r="J106" s="42"/>
       <c r="K106" s="44"/>
       <c r="L106" s="42"/>
@@ -6185,12 +6186,12 @@
       <c r="A107" s="32"/>
       <c r="B107" s="42"/>
       <c r="C107" s="42"/>
-      <c r="D107" s="44"/>
-      <c r="E107" s="42"/>
+      <c r="D107" s="42"/>
+      <c r="E107" s="44"/>
       <c r="F107" s="42"/>
-      <c r="G107" s="44"/>
+      <c r="G107" s="42"/>
       <c r="H107" s="44"/>
-      <c r="I107" s="42"/>
+      <c r="I107" s="44"/>
       <c r="J107" s="42"/>
       <c r="K107" s="44"/>
       <c r="L107" s="42"/>
@@ -6211,12 +6212,12 @@
       <c r="A108" s="32"/>
       <c r="B108" s="42"/>
       <c r="C108" s="42"/>
-      <c r="D108" s="44"/>
-      <c r="E108" s="42"/>
+      <c r="D108" s="42"/>
+      <c r="E108" s="44"/>
       <c r="F108" s="42"/>
-      <c r="G108" s="44"/>
+      <c r="G108" s="42"/>
       <c r="H108" s="44"/>
-      <c r="I108" s="42"/>
+      <c r="I108" s="44"/>
       <c r="J108" s="42"/>
       <c r="K108" s="44"/>
       <c r="L108" s="42"/>
@@ -6237,12 +6238,12 @@
       <c r="A109" s="32"/>
       <c r="B109" s="42"/>
       <c r="C109" s="42"/>
-      <c r="D109" s="44"/>
-      <c r="E109" s="42"/>
+      <c r="D109" s="42"/>
+      <c r="E109" s="44"/>
       <c r="F109" s="42"/>
-      <c r="G109" s="44"/>
+      <c r="G109" s="42"/>
       <c r="H109" s="44"/>
-      <c r="I109" s="42"/>
+      <c r="I109" s="44"/>
       <c r="J109" s="42"/>
       <c r="K109" s="44"/>
       <c r="L109" s="42"/>
@@ -6263,12 +6264,12 @@
       <c r="A110" s="32"/>
       <c r="B110" s="42"/>
       <c r="C110" s="42"/>
-      <c r="D110" s="44"/>
-      <c r="E110" s="42"/>
+      <c r="D110" s="42"/>
+      <c r="E110" s="44"/>
       <c r="F110" s="42"/>
-      <c r="G110" s="44"/>
+      <c r="G110" s="42"/>
       <c r="H110" s="44"/>
-      <c r="I110" s="42"/>
+      <c r="I110" s="44"/>
       <c r="J110" s="42"/>
       <c r="K110" s="44"/>
       <c r="L110" s="42"/>
@@ -6289,12 +6290,12 @@
       <c r="A111" s="32"/>
       <c r="B111" s="42"/>
       <c r="C111" s="42"/>
-      <c r="D111" s="44"/>
-      <c r="E111" s="42"/>
+      <c r="D111" s="42"/>
+      <c r="E111" s="44"/>
       <c r="F111" s="42"/>
-      <c r="G111" s="44"/>
+      <c r="G111" s="42"/>
       <c r="H111" s="44"/>
-      <c r="I111" s="42"/>
+      <c r="I111" s="44"/>
       <c r="J111" s="42"/>
       <c r="K111" s="44"/>
       <c r="L111" s="42"/>
@@ -6315,12 +6316,12 @@
       <c r="A112" s="32"/>
       <c r="B112" s="42"/>
       <c r="C112" s="42"/>
-      <c r="D112" s="44"/>
-      <c r="E112" s="42"/>
+      <c r="D112" s="42"/>
+      <c r="E112" s="44"/>
       <c r="F112" s="42"/>
-      <c r="G112" s="44"/>
+      <c r="G112" s="42"/>
       <c r="H112" s="44"/>
-      <c r="I112" s="42"/>
+      <c r="I112" s="44"/>
       <c r="J112" s="42"/>
       <c r="K112" s="44"/>
       <c r="L112" s="42"/>
@@ -6341,12 +6342,12 @@
       <c r="A113" s="32"/>
       <c r="B113" s="42"/>
       <c r="C113" s="42"/>
-      <c r="D113" s="44"/>
-      <c r="E113" s="42"/>
+      <c r="D113" s="42"/>
+      <c r="E113" s="44"/>
       <c r="F113" s="42"/>
-      <c r="G113" s="44"/>
+      <c r="G113" s="42"/>
       <c r="H113" s="44"/>
-      <c r="I113" s="42"/>
+      <c r="I113" s="44"/>
       <c r="J113" s="42"/>
       <c r="K113" s="44"/>
       <c r="L113" s="42"/>
@@ -6367,12 +6368,12 @@
       <c r="A114" s="32"/>
       <c r="B114" s="42"/>
       <c r="C114" s="42"/>
-      <c r="D114" s="44"/>
-      <c r="E114" s="42"/>
+      <c r="D114" s="42"/>
+      <c r="E114" s="44"/>
       <c r="F114" s="42"/>
-      <c r="G114" s="44"/>
+      <c r="G114" s="42"/>
       <c r="H114" s="44"/>
-      <c r="I114" s="42"/>
+      <c r="I114" s="44"/>
       <c r="J114" s="42"/>
       <c r="K114" s="44"/>
       <c r="L114" s="42"/>
@@ -6393,12 +6394,12 @@
       <c r="A115" s="32"/>
       <c r="B115" s="42"/>
       <c r="C115" s="42"/>
-      <c r="D115" s="44"/>
-      <c r="E115" s="42"/>
+      <c r="D115" s="42"/>
+      <c r="E115" s="44"/>
       <c r="F115" s="42"/>
-      <c r="G115" s="44"/>
+      <c r="G115" s="42"/>
       <c r="H115" s="44"/>
-      <c r="I115" s="42"/>
+      <c r="I115" s="44"/>
       <c r="J115" s="42"/>
       <c r="K115" s="44"/>
       <c r="L115" s="42"/>
@@ -6419,12 +6420,12 @@
       <c r="A116" s="32"/>
       <c r="B116" s="42"/>
       <c r="C116" s="42"/>
-      <c r="D116" s="44"/>
-      <c r="E116" s="42"/>
+      <c r="D116" s="42"/>
+      <c r="E116" s="44"/>
       <c r="F116" s="42"/>
-      <c r="G116" s="44"/>
+      <c r="G116" s="42"/>
       <c r="H116" s="44"/>
-      <c r="I116" s="42"/>
+      <c r="I116" s="44"/>
       <c r="J116" s="42"/>
       <c r="K116" s="44"/>
       <c r="L116" s="42"/>
@@ -6445,12 +6446,12 @@
       <c r="A117" s="32"/>
       <c r="B117" s="42"/>
       <c r="C117" s="42"/>
-      <c r="D117" s="44"/>
-      <c r="E117" s="42"/>
+      <c r="D117" s="42"/>
+      <c r="E117" s="44"/>
       <c r="F117" s="42"/>
-      <c r="G117" s="44"/>
+      <c r="G117" s="42"/>
       <c r="H117" s="44"/>
-      <c r="I117" s="42"/>
+      <c r="I117" s="44"/>
       <c r="J117" s="42"/>
       <c r="K117" s="44"/>
       <c r="L117" s="42"/>
@@ -6471,12 +6472,12 @@
       <c r="A118" s="32"/>
       <c r="B118" s="42"/>
       <c r="C118" s="42"/>
-      <c r="D118" s="44"/>
-      <c r="E118" s="42"/>
+      <c r="D118" s="42"/>
+      <c r="E118" s="44"/>
       <c r="F118" s="42"/>
-      <c r="G118" s="44"/>
+      <c r="G118" s="42"/>
       <c r="H118" s="44"/>
-      <c r="I118" s="42"/>
+      <c r="I118" s="44"/>
       <c r="J118" s="42"/>
       <c r="K118" s="44"/>
       <c r="L118" s="42"/>
@@ -6497,12 +6498,12 @@
       <c r="A119" s="32"/>
       <c r="B119" s="42"/>
       <c r="C119" s="42"/>
-      <c r="D119" s="44"/>
-      <c r="E119" s="42"/>
+      <c r="D119" s="42"/>
+      <c r="E119" s="44"/>
       <c r="F119" s="42"/>
-      <c r="G119" s="44"/>
+      <c r="G119" s="42"/>
       <c r="H119" s="44"/>
-      <c r="I119" s="42"/>
+      <c r="I119" s="44"/>
       <c r="J119" s="42"/>
       <c r="K119" s="44"/>
       <c r="L119" s="42"/>
@@ -6523,12 +6524,12 @@
       <c r="A120" s="32"/>
       <c r="B120" s="42"/>
       <c r="C120" s="42"/>
-      <c r="D120" s="44"/>
-      <c r="E120" s="42"/>
+      <c r="D120" s="42"/>
+      <c r="E120" s="44"/>
       <c r="F120" s="42"/>
-      <c r="G120" s="44"/>
+      <c r="G120" s="42"/>
       <c r="H120" s="44"/>
-      <c r="I120" s="42"/>
+      <c r="I120" s="44"/>
       <c r="J120" s="42"/>
       <c r="K120" s="44"/>
       <c r="L120" s="42"/>
@@ -6549,12 +6550,12 @@
       <c r="A121" s="32"/>
       <c r="B121" s="42"/>
       <c r="C121" s="42"/>
-      <c r="D121" s="44"/>
-      <c r="E121" s="42"/>
+      <c r="D121" s="42"/>
+      <c r="E121" s="44"/>
       <c r="F121" s="42"/>
-      <c r="G121" s="44"/>
+      <c r="G121" s="42"/>
       <c r="H121" s="44"/>
-      <c r="I121" s="42"/>
+      <c r="I121" s="44"/>
       <c r="J121" s="42"/>
       <c r="K121" s="44"/>
       <c r="L121" s="42"/>
@@ -6575,12 +6576,12 @@
       <c r="A122" s="32"/>
       <c r="B122" s="42"/>
       <c r="C122" s="42"/>
-      <c r="D122" s="44"/>
-      <c r="E122" s="42"/>
+      <c r="D122" s="42"/>
+      <c r="E122" s="44"/>
       <c r="F122" s="42"/>
-      <c r="G122" s="44"/>
+      <c r="G122" s="42"/>
       <c r="H122" s="44"/>
-      <c r="I122" s="42"/>
+      <c r="I122" s="44"/>
       <c r="J122" s="42"/>
       <c r="K122" s="44"/>
       <c r="L122" s="42"/>
@@ -6601,12 +6602,12 @@
       <c r="A123" s="32"/>
       <c r="B123" s="42"/>
       <c r="C123" s="42"/>
-      <c r="D123" s="44"/>
-      <c r="E123" s="42"/>
+      <c r="D123" s="42"/>
+      <c r="E123" s="44"/>
       <c r="F123" s="42"/>
-      <c r="G123" s="44"/>
+      <c r="G123" s="42"/>
       <c r="H123" s="44"/>
-      <c r="I123" s="42"/>
+      <c r="I123" s="44"/>
       <c r="J123" s="42"/>
       <c r="K123" s="44"/>
       <c r="L123" s="42"/>
@@ -6627,12 +6628,12 @@
       <c r="A124" s="32"/>
       <c r="B124" s="42"/>
       <c r="C124" s="42"/>
-      <c r="D124" s="44"/>
-      <c r="E124" s="42"/>
+      <c r="D124" s="42"/>
+      <c r="E124" s="44"/>
       <c r="F124" s="42"/>
-      <c r="G124" s="44"/>
+      <c r="G124" s="42"/>
       <c r="H124" s="44"/>
-      <c r="I124" s="42"/>
+      <c r="I124" s="44"/>
       <c r="J124" s="42"/>
       <c r="K124" s="44"/>
       <c r="L124" s="42"/>
@@ -6653,12 +6654,12 @@
       <c r="A125" s="32"/>
       <c r="B125" s="42"/>
       <c r="C125" s="42"/>
-      <c r="D125" s="44"/>
-      <c r="E125" s="42"/>
+      <c r="D125" s="42"/>
+      <c r="E125" s="44"/>
       <c r="F125" s="42"/>
-      <c r="G125" s="44"/>
+      <c r="G125" s="42"/>
       <c r="H125" s="44"/>
-      <c r="I125" s="42"/>
+      <c r="I125" s="44"/>
       <c r="J125" s="42"/>
       <c r="K125" s="44"/>
       <c r="L125" s="42"/>
@@ -6679,12 +6680,12 @@
       <c r="A126" s="32"/>
       <c r="B126" s="42"/>
       <c r="C126" s="42"/>
-      <c r="D126" s="44"/>
-      <c r="E126" s="42"/>
+      <c r="D126" s="42"/>
+      <c r="E126" s="44"/>
       <c r="F126" s="42"/>
-      <c r="G126" s="44"/>
+      <c r="G126" s="42"/>
       <c r="H126" s="44"/>
-      <c r="I126" s="42"/>
+      <c r="I126" s="44"/>
       <c r="J126" s="42"/>
       <c r="K126" s="44"/>
       <c r="L126" s="42"/>
@@ -6705,12 +6706,12 @@
       <c r="A127" s="32"/>
       <c r="B127" s="42"/>
       <c r="C127" s="42"/>
-      <c r="D127" s="44"/>
-      <c r="E127" s="42"/>
+      <c r="D127" s="42"/>
+      <c r="E127" s="44"/>
       <c r="F127" s="42"/>
-      <c r="G127" s="44"/>
+      <c r="G127" s="42"/>
       <c r="H127" s="44"/>
-      <c r="I127" s="42"/>
+      <c r="I127" s="44"/>
       <c r="J127" s="42"/>
       <c r="K127" s="44"/>
       <c r="L127" s="42"/>
@@ -6731,12 +6732,12 @@
       <c r="A128" s="32"/>
       <c r="B128" s="42"/>
       <c r="C128" s="42"/>
-      <c r="D128" s="44"/>
-      <c r="E128" s="42"/>
+      <c r="D128" s="42"/>
+      <c r="E128" s="44"/>
       <c r="F128" s="42"/>
-      <c r="G128" s="44"/>
+      <c r="G128" s="42"/>
       <c r="H128" s="44"/>
-      <c r="I128" s="42"/>
+      <c r="I128" s="44"/>
       <c r="J128" s="42"/>
       <c r="K128" s="44"/>
       <c r="L128" s="42"/>
@@ -6757,12 +6758,12 @@
       <c r="A129" s="32"/>
       <c r="B129" s="42"/>
       <c r="C129" s="42"/>
-      <c r="D129" s="44"/>
-      <c r="E129" s="42"/>
+      <c r="D129" s="42"/>
+      <c r="E129" s="44"/>
       <c r="F129" s="42"/>
-      <c r="G129" s="44"/>
+      <c r="G129" s="42"/>
       <c r="H129" s="44"/>
-      <c r="I129" s="42"/>
+      <c r="I129" s="44"/>
       <c r="J129" s="42"/>
       <c r="K129" s="44"/>
       <c r="L129" s="42"/>
@@ -6783,12 +6784,12 @@
       <c r="A130" s="32"/>
       <c r="B130" s="42"/>
       <c r="C130" s="42"/>
-      <c r="D130" s="44"/>
-      <c r="E130" s="42"/>
+      <c r="D130" s="42"/>
+      <c r="E130" s="44"/>
       <c r="F130" s="42"/>
-      <c r="G130" s="44"/>
+      <c r="G130" s="42"/>
       <c r="H130" s="44"/>
-      <c r="I130" s="42"/>
+      <c r="I130" s="44"/>
       <c r="J130" s="42"/>
       <c r="K130" s="44"/>
       <c r="L130" s="42"/>
@@ -6809,12 +6810,12 @@
       <c r="A131" s="32"/>
       <c r="B131" s="42"/>
       <c r="C131" s="42"/>
-      <c r="D131" s="44"/>
-      <c r="E131" s="42"/>
+      <c r="D131" s="42"/>
+      <c r="E131" s="44"/>
       <c r="F131" s="42"/>
-      <c r="G131" s="44"/>
+      <c r="G131" s="42"/>
       <c r="H131" s="44"/>
-      <c r="I131" s="42"/>
+      <c r="I131" s="44"/>
       <c r="J131" s="42"/>
       <c r="K131" s="44"/>
       <c r="L131" s="42"/>
@@ -6835,12 +6836,12 @@
       <c r="A132" s="32"/>
       <c r="B132" s="42"/>
       <c r="C132" s="42"/>
-      <c r="D132" s="44"/>
-      <c r="E132" s="42"/>
+      <c r="D132" s="42"/>
+      <c r="E132" s="44"/>
       <c r="F132" s="42"/>
-      <c r="G132" s="44"/>
+      <c r="G132" s="42"/>
       <c r="H132" s="44"/>
-      <c r="I132" s="42"/>
+      <c r="I132" s="44"/>
       <c r="J132" s="42"/>
       <c r="K132" s="44"/>
       <c r="L132" s="42"/>
@@ -6861,12 +6862,12 @@
       <c r="A133" s="32"/>
       <c r="B133" s="42"/>
       <c r="C133" s="42"/>
-      <c r="D133" s="44"/>
-      <c r="E133" s="42"/>
+      <c r="D133" s="42"/>
+      <c r="E133" s="44"/>
       <c r="F133" s="42"/>
-      <c r="G133" s="44"/>
+      <c r="G133" s="42"/>
       <c r="H133" s="44"/>
-      <c r="I133" s="42"/>
+      <c r="I133" s="44"/>
       <c r="J133" s="42"/>
       <c r="K133" s="44"/>
       <c r="L133" s="42"/>
@@ -6887,12 +6888,12 @@
       <c r="A134" s="32"/>
       <c r="B134" s="42"/>
       <c r="C134" s="42"/>
-      <c r="D134" s="44"/>
-      <c r="E134" s="42"/>
+      <c r="D134" s="42"/>
+      <c r="E134" s="44"/>
       <c r="F134" s="42"/>
-      <c r="G134" s="44"/>
+      <c r="G134" s="42"/>
       <c r="H134" s="44"/>
-      <c r="I134" s="42"/>
+      <c r="I134" s="44"/>
       <c r="J134" s="42"/>
       <c r="K134" s="44"/>
       <c r="L134" s="42"/>
@@ -6913,12 +6914,12 @@
       <c r="A135" s="32"/>
       <c r="B135" s="42"/>
       <c r="C135" s="42"/>
-      <c r="D135" s="44"/>
-      <c r="E135" s="42"/>
+      <c r="D135" s="42"/>
+      <c r="E135" s="44"/>
       <c r="F135" s="42"/>
-      <c r="G135" s="44"/>
+      <c r="G135" s="42"/>
       <c r="H135" s="44"/>
-      <c r="I135" s="42"/>
+      <c r="I135" s="44"/>
       <c r="J135" s="42"/>
       <c r="K135" s="44"/>
       <c r="L135" s="42"/>
@@ -6939,12 +6940,12 @@
       <c r="A136" s="32"/>
       <c r="B136" s="42"/>
       <c r="C136" s="42"/>
-      <c r="D136" s="44"/>
-      <c r="E136" s="42"/>
+      <c r="D136" s="42"/>
+      <c r="E136" s="44"/>
       <c r="F136" s="42"/>
-      <c r="G136" s="44"/>
+      <c r="G136" s="42"/>
       <c r="H136" s="44"/>
-      <c r="I136" s="42"/>
+      <c r="I136" s="44"/>
       <c r="J136" s="42"/>
       <c r="K136" s="44"/>
       <c r="L136" s="42"/>
@@ -6965,12 +6966,12 @@
       <c r="A137" s="32"/>
       <c r="B137" s="42"/>
       <c r="C137" s="42"/>
-      <c r="D137" s="44"/>
-      <c r="E137" s="42"/>
+      <c r="D137" s="42"/>
+      <c r="E137" s="44"/>
       <c r="F137" s="42"/>
-      <c r="G137" s="44"/>
+      <c r="G137" s="42"/>
       <c r="H137" s="44"/>
-      <c r="I137" s="42"/>
+      <c r="I137" s="44"/>
       <c r="J137" s="42"/>
       <c r="K137" s="44"/>
       <c r="L137" s="42"/>
@@ -6991,12 +6992,12 @@
       <c r="A138" s="32"/>
       <c r="B138" s="42"/>
       <c r="C138" s="42"/>
-      <c r="D138" s="44"/>
-      <c r="E138" s="42"/>
+      <c r="D138" s="42"/>
+      <c r="E138" s="44"/>
       <c r="F138" s="42"/>
-      <c r="G138" s="44"/>
+      <c r="G138" s="42"/>
       <c r="H138" s="44"/>
-      <c r="I138" s="42"/>
+      <c r="I138" s="44"/>
       <c r="J138" s="42"/>
       <c r="K138" s="44"/>
       <c r="L138" s="42"/>
@@ -7017,12 +7018,12 @@
       <c r="A139" s="32"/>
       <c r="B139" s="42"/>
       <c r="C139" s="42"/>
-      <c r="D139" s="44"/>
-      <c r="E139" s="42"/>
+      <c r="D139" s="42"/>
+      <c r="E139" s="44"/>
       <c r="F139" s="42"/>
-      <c r="G139" s="44"/>
+      <c r="G139" s="42"/>
       <c r="H139" s="44"/>
-      <c r="I139" s="42"/>
+      <c r="I139" s="44"/>
       <c r="J139" s="42"/>
       <c r="K139" s="44"/>
       <c r="L139" s="42"/>
@@ -7043,12 +7044,12 @@
       <c r="A140" s="32"/>
       <c r="B140" s="42"/>
       <c r="C140" s="42"/>
-      <c r="D140" s="44"/>
-      <c r="E140" s="42"/>
+      <c r="D140" s="42"/>
+      <c r="E140" s="44"/>
       <c r="F140" s="42"/>
-      <c r="G140" s="44"/>
+      <c r="G140" s="42"/>
       <c r="H140" s="44"/>
-      <c r="I140" s="42"/>
+      <c r="I140" s="44"/>
       <c r="J140" s="42"/>
       <c r="K140" s="44"/>
       <c r="L140" s="42"/>
@@ -7069,12 +7070,12 @@
       <c r="A141" s="32"/>
       <c r="B141" s="42"/>
       <c r="C141" s="42"/>
-      <c r="D141" s="44"/>
-      <c r="E141" s="42"/>
+      <c r="D141" s="42"/>
+      <c r="E141" s="44"/>
       <c r="F141" s="42"/>
-      <c r="G141" s="44"/>
+      <c r="G141" s="42"/>
       <c r="H141" s="44"/>
-      <c r="I141" s="42"/>
+      <c r="I141" s="44"/>
       <c r="J141" s="42"/>
       <c r="K141" s="44"/>
       <c r="L141" s="42"/>
@@ -7095,12 +7096,12 @@
       <c r="A142" s="32"/>
       <c r="B142" s="42"/>
       <c r="C142" s="42"/>
-      <c r="D142" s="44"/>
-      <c r="E142" s="42"/>
+      <c r="D142" s="42"/>
+      <c r="E142" s="44"/>
       <c r="F142" s="42"/>
-      <c r="G142" s="44"/>
+      <c r="G142" s="42"/>
       <c r="H142" s="44"/>
-      <c r="I142" s="42"/>
+      <c r="I142" s="44"/>
       <c r="J142" s="42"/>
       <c r="K142" s="44"/>
       <c r="L142" s="42"/>
@@ -7121,12 +7122,12 @@
       <c r="A143" s="32"/>
       <c r="B143" s="42"/>
       <c r="C143" s="42"/>
-      <c r="D143" s="44"/>
-      <c r="E143" s="42"/>
+      <c r="D143" s="42"/>
+      <c r="E143" s="44"/>
       <c r="F143" s="42"/>
-      <c r="G143" s="44"/>
+      <c r="G143" s="42"/>
       <c r="H143" s="44"/>
-      <c r="I143" s="42"/>
+      <c r="I143" s="44"/>
       <c r="J143" s="42"/>
       <c r="K143" s="44"/>
       <c r="L143" s="42"/>
@@ -7147,12 +7148,12 @@
       <c r="A144" s="32"/>
       <c r="B144" s="42"/>
       <c r="C144" s="42"/>
-      <c r="D144" s="44"/>
-      <c r="E144" s="42"/>
+      <c r="D144" s="42"/>
+      <c r="E144" s="44"/>
       <c r="F144" s="42"/>
-      <c r="G144" s="44"/>
+      <c r="G144" s="42"/>
       <c r="H144" s="44"/>
-      <c r="I144" s="42"/>
+      <c r="I144" s="44"/>
       <c r="J144" s="42"/>
       <c r="K144" s="44"/>
       <c r="L144" s="42"/>
@@ -7173,12 +7174,12 @@
       <c r="A145" s="32"/>
       <c r="B145" s="42"/>
       <c r="C145" s="42"/>
-      <c r="D145" s="44"/>
-      <c r="E145" s="42"/>
+      <c r="D145" s="42"/>
+      <c r="E145" s="44"/>
       <c r="F145" s="42"/>
-      <c r="G145" s="44"/>
+      <c r="G145" s="42"/>
       <c r="H145" s="44"/>
-      <c r="I145" s="42"/>
+      <c r="I145" s="44"/>
       <c r="J145" s="42"/>
       <c r="K145" s="44"/>
       <c r="L145" s="42"/>
@@ -7199,12 +7200,12 @@
       <c r="A146" s="32"/>
       <c r="B146" s="42"/>
       <c r="C146" s="42"/>
-      <c r="D146" s="44"/>
-      <c r="E146" s="42"/>
+      <c r="D146" s="42"/>
+      <c r="E146" s="44"/>
       <c r="F146" s="42"/>
-      <c r="G146" s="44"/>
+      <c r="G146" s="42"/>
       <c r="H146" s="44"/>
-      <c r="I146" s="42"/>
+      <c r="I146" s="44"/>
       <c r="J146" s="42"/>
       <c r="K146" s="44"/>
       <c r="L146" s="42"/>
@@ -7225,12 +7226,12 @@
       <c r="A147" s="32"/>
       <c r="B147" s="42"/>
       <c r="C147" s="42"/>
-      <c r="D147" s="44"/>
-      <c r="E147" s="42"/>
+      <c r="D147" s="42"/>
+      <c r="E147" s="44"/>
       <c r="F147" s="42"/>
-      <c r="G147" s="44"/>
+      <c r="G147" s="42"/>
       <c r="H147" s="44"/>
-      <c r="I147" s="42"/>
+      <c r="I147" s="44"/>
       <c r="J147" s="42"/>
       <c r="K147" s="44"/>
       <c r="L147" s="42"/>
@@ -7251,12 +7252,12 @@
       <c r="A148" s="32"/>
       <c r="B148" s="42"/>
       <c r="C148" s="42"/>
-      <c r="D148" s="44"/>
-      <c r="E148" s="42"/>
+      <c r="D148" s="42"/>
+      <c r="E148" s="44"/>
       <c r="F148" s="42"/>
-      <c r="G148" s="44"/>
+      <c r="G148" s="42"/>
       <c r="H148" s="44"/>
-      <c r="I148" s="42"/>
+      <c r="I148" s="44"/>
       <c r="J148" s="42"/>
       <c r="K148" s="44"/>
       <c r="L148" s="42"/>
@@ -7277,12 +7278,12 @@
       <c r="A149" s="32"/>
       <c r="B149" s="42"/>
       <c r="C149" s="42"/>
-      <c r="D149" s="44"/>
-      <c r="E149" s="42"/>
+      <c r="D149" s="42"/>
+      <c r="E149" s="44"/>
       <c r="F149" s="42"/>
-      <c r="G149" s="44"/>
+      <c r="G149" s="42"/>
       <c r="H149" s="44"/>
-      <c r="I149" s="42"/>
+      <c r="I149" s="44"/>
       <c r="J149" s="42"/>
       <c r="K149" s="44"/>
       <c r="L149" s="42"/>
@@ -7303,12 +7304,12 @@
       <c r="A150" s="32"/>
       <c r="B150" s="42"/>
       <c r="C150" s="42"/>
-      <c r="D150" s="44"/>
-      <c r="E150" s="42"/>
+      <c r="D150" s="42"/>
+      <c r="E150" s="44"/>
       <c r="F150" s="42"/>
-      <c r="G150" s="44"/>
+      <c r="G150" s="42"/>
       <c r="H150" s="44"/>
-      <c r="I150" s="42"/>
+      <c r="I150" s="44"/>
       <c r="J150" s="42"/>
       <c r="K150" s="44"/>
       <c r="L150" s="42"/>
@@ -7329,12 +7330,12 @@
       <c r="A151" s="32"/>
       <c r="B151" s="42"/>
       <c r="C151" s="42"/>
-      <c r="D151" s="44"/>
-      <c r="E151" s="42"/>
+      <c r="D151" s="42"/>
+      <c r="E151" s="44"/>
       <c r="F151" s="42"/>
-      <c r="G151" s="44"/>
+      <c r="G151" s="42"/>
       <c r="H151" s="44"/>
-      <c r="I151" s="42"/>
+      <c r="I151" s="44"/>
       <c r="J151" s="42"/>
       <c r="K151" s="44"/>
       <c r="L151" s="42"/>
@@ -7355,12 +7356,12 @@
       <c r="A152" s="32"/>
       <c r="B152" s="42"/>
       <c r="C152" s="42"/>
-      <c r="D152" s="44"/>
-      <c r="E152" s="42"/>
+      <c r="D152" s="42"/>
+      <c r="E152" s="44"/>
       <c r="F152" s="42"/>
-      <c r="G152" s="44"/>
+      <c r="G152" s="42"/>
       <c r="H152" s="44"/>
-      <c r="I152" s="42"/>
+      <c r="I152" s="44"/>
       <c r="J152" s="42"/>
       <c r="K152" s="44"/>
       <c r="L152" s="42"/>
@@ -7381,12 +7382,12 @@
       <c r="A153" s="32"/>
       <c r="B153" s="42"/>
       <c r="C153" s="42"/>
-      <c r="D153" s="44"/>
-      <c r="E153" s="42"/>
+      <c r="D153" s="42"/>
+      <c r="E153" s="44"/>
       <c r="F153" s="42"/>
-      <c r="G153" s="44"/>
+      <c r="G153" s="42"/>
       <c r="H153" s="44"/>
-      <c r="I153" s="42"/>
+      <c r="I153" s="44"/>
       <c r="J153" s="42"/>
       <c r="K153" s="44"/>
       <c r="L153" s="42"/>
@@ -7407,12 +7408,12 @@
       <c r="A154" s="32"/>
       <c r="B154" s="42"/>
       <c r="C154" s="42"/>
-      <c r="D154" s="44"/>
-      <c r="E154" s="42"/>
+      <c r="D154" s="42"/>
+      <c r="E154" s="44"/>
       <c r="F154" s="42"/>
-      <c r="G154" s="44"/>
+      <c r="G154" s="42"/>
       <c r="H154" s="44"/>
-      <c r="I154" s="42"/>
+      <c r="I154" s="44"/>
       <c r="J154" s="42"/>
       <c r="K154" s="44"/>
       <c r="L154" s="42"/>
@@ -7433,12 +7434,12 @@
       <c r="A155" s="32"/>
       <c r="B155" s="42"/>
       <c r="C155" s="42"/>
-      <c r="D155" s="44"/>
-      <c r="E155" s="42"/>
+      <c r="D155" s="42"/>
+      <c r="E155" s="44"/>
       <c r="F155" s="42"/>
-      <c r="G155" s="44"/>
+      <c r="G155" s="42"/>
       <c r="H155" s="44"/>
-      <c r="I155" s="42"/>
+      <c r="I155" s="44"/>
       <c r="J155" s="42"/>
       <c r="K155" s="44"/>
       <c r="L155" s="42"/>
@@ -7459,12 +7460,12 @@
       <c r="A156" s="32"/>
       <c r="B156" s="42"/>
       <c r="C156" s="42"/>
-      <c r="D156" s="44"/>
-      <c r="E156" s="42"/>
+      <c r="D156" s="42"/>
+      <c r="E156" s="44"/>
       <c r="F156" s="42"/>
-      <c r="G156" s="44"/>
+      <c r="G156" s="42"/>
       <c r="H156" s="44"/>
-      <c r="I156" s="42"/>
+      <c r="I156" s="44"/>
       <c r="J156" s="42"/>
       <c r="K156" s="44"/>
       <c r="L156" s="42"/>
@@ -7485,12 +7486,12 @@
       <c r="A157" s="32"/>
       <c r="B157" s="42"/>
       <c r="C157" s="42"/>
-      <c r="D157" s="44"/>
-      <c r="E157" s="42"/>
+      <c r="D157" s="42"/>
+      <c r="E157" s="44"/>
       <c r="F157" s="42"/>
-      <c r="G157" s="44"/>
+      <c r="G157" s="42"/>
       <c r="H157" s="44"/>
-      <c r="I157" s="42"/>
+      <c r="I157" s="44"/>
       <c r="J157" s="42"/>
       <c r="K157" s="44"/>
       <c r="L157" s="42"/>
@@ -7511,12 +7512,12 @@
       <c r="A158" s="32"/>
       <c r="B158" s="42"/>
       <c r="C158" s="42"/>
-      <c r="D158" s="44"/>
-      <c r="E158" s="42"/>
+      <c r="D158" s="42"/>
+      <c r="E158" s="44"/>
       <c r="F158" s="42"/>
-      <c r="G158" s="44"/>
+      <c r="G158" s="42"/>
       <c r="H158" s="44"/>
-      <c r="I158" s="42"/>
+      <c r="I158" s="44"/>
       <c r="J158" s="42"/>
       <c r="K158" s="44"/>
       <c r="L158" s="42"/>
@@ -7537,12 +7538,12 @@
       <c r="A159" s="32"/>
       <c r="B159" s="42"/>
       <c r="C159" s="42"/>
-      <c r="D159" s="44"/>
-      <c r="E159" s="42"/>
+      <c r="D159" s="42"/>
+      <c r="E159" s="44"/>
       <c r="F159" s="42"/>
-      <c r="G159" s="44"/>
+      <c r="G159" s="42"/>
       <c r="H159" s="44"/>
-      <c r="I159" s="42"/>
+      <c r="I159" s="44"/>
       <c r="J159" s="42"/>
       <c r="K159" s="44"/>
       <c r="L159" s="42"/>
@@ -7563,12 +7564,12 @@
       <c r="A160" s="32"/>
       <c r="B160" s="42"/>
       <c r="C160" s="42"/>
-      <c r="D160" s="44"/>
-      <c r="E160" s="42"/>
+      <c r="D160" s="42"/>
+      <c r="E160" s="44"/>
       <c r="F160" s="42"/>
-      <c r="G160" s="44"/>
+      <c r="G160" s="42"/>
       <c r="H160" s="44"/>
-      <c r="I160" s="42"/>
+      <c r="I160" s="44"/>
       <c r="J160" s="42"/>
       <c r="K160" s="44"/>
       <c r="L160" s="42"/>
@@ -7589,12 +7590,12 @@
       <c r="A161" s="32"/>
       <c r="B161" s="42"/>
       <c r="C161" s="42"/>
-      <c r="D161" s="44"/>
-      <c r="E161" s="42"/>
+      <c r="D161" s="42"/>
+      <c r="E161" s="44"/>
       <c r="F161" s="42"/>
-      <c r="G161" s="44"/>
+      <c r="G161" s="42"/>
       <c r="H161" s="44"/>
-      <c r="I161" s="42"/>
+      <c r="I161" s="44"/>
       <c r="J161" s="42"/>
       <c r="K161" s="44"/>
       <c r="L161" s="42"/>
@@ -7615,12 +7616,12 @@
       <c r="A162" s="32"/>
       <c r="B162" s="42"/>
       <c r="C162" s="42"/>
-      <c r="D162" s="44"/>
-      <c r="E162" s="42"/>
+      <c r="D162" s="42"/>
+      <c r="E162" s="44"/>
       <c r="F162" s="42"/>
-      <c r="G162" s="44"/>
+      <c r="G162" s="42"/>
       <c r="H162" s="44"/>
-      <c r="I162" s="42"/>
+      <c r="I162" s="44"/>
       <c r="J162" s="42"/>
       <c r="K162" s="44"/>
       <c r="L162" s="42"/>
@@ -7641,12 +7642,12 @@
       <c r="A163" s="32"/>
       <c r="B163" s="42"/>
       <c r="C163" s="42"/>
-      <c r="D163" s="44"/>
-      <c r="E163" s="42"/>
+      <c r="D163" s="42"/>
+      <c r="E163" s="44"/>
       <c r="F163" s="42"/>
-      <c r="G163" s="44"/>
+      <c r="G163" s="42"/>
       <c r="H163" s="44"/>
-      <c r="I163" s="42"/>
+      <c r="I163" s="44"/>
       <c r="J163" s="42"/>
       <c r="K163" s="44"/>
       <c r="L163" s="42"/>
@@ -7667,12 +7668,12 @@
       <c r="A164" s="32"/>
       <c r="B164" s="42"/>
       <c r="C164" s="42"/>
-      <c r="D164" s="44"/>
-      <c r="E164" s="42"/>
+      <c r="D164" s="42"/>
+      <c r="E164" s="44"/>
       <c r="F164" s="42"/>
-      <c r="G164" s="44"/>
+      <c r="G164" s="42"/>
       <c r="H164" s="44"/>
-      <c r="I164" s="42"/>
+      <c r="I164" s="44"/>
       <c r="J164" s="42"/>
       <c r="K164" s="44"/>
       <c r="L164" s="42"/>
@@ -7693,12 +7694,12 @@
       <c r="A165" s="32"/>
       <c r="B165" s="42"/>
       <c r="C165" s="42"/>
-      <c r="D165" s="44"/>
-      <c r="E165" s="42"/>
+      <c r="D165" s="42"/>
+      <c r="E165" s="44"/>
       <c r="F165" s="42"/>
-      <c r="G165" s="44"/>
+      <c r="G165" s="42"/>
       <c r="H165" s="44"/>
-      <c r="I165" s="42"/>
+      <c r="I165" s="44"/>
       <c r="J165" s="42"/>
       <c r="K165" s="44"/>
       <c r="L165" s="42"/>
@@ -7719,12 +7720,12 @@
       <c r="A166" s="32"/>
       <c r="B166" s="42"/>
       <c r="C166" s="42"/>
-      <c r="D166" s="44"/>
-      <c r="E166" s="42"/>
+      <c r="D166" s="42"/>
+      <c r="E166" s="44"/>
       <c r="F166" s="42"/>
-      <c r="G166" s="44"/>
+      <c r="G166" s="42"/>
       <c r="H166" s="44"/>
-      <c r="I166" s="42"/>
+      <c r="I166" s="44"/>
       <c r="J166" s="42"/>
       <c r="K166" s="44"/>
       <c r="L166" s="42"/>
@@ -7745,12 +7746,12 @@
       <c r="A167" s="32"/>
       <c r="B167" s="42"/>
       <c r="C167" s="42"/>
-      <c r="D167" s="44"/>
-      <c r="E167" s="42"/>
+      <c r="D167" s="42"/>
+      <c r="E167" s="44"/>
       <c r="F167" s="42"/>
-      <c r="G167" s="44"/>
+      <c r="G167" s="42"/>
       <c r="H167" s="44"/>
-      <c r="I167" s="42"/>
+      <c r="I167" s="44"/>
       <c r="J167" s="42"/>
       <c r="K167" s="44"/>
       <c r="L167" s="42"/>
@@ -7771,12 +7772,12 @@
       <c r="A168" s="32"/>
       <c r="B168" s="42"/>
       <c r="C168" s="42"/>
-      <c r="D168" s="44"/>
-      <c r="E168" s="42"/>
+      <c r="D168" s="42"/>
+      <c r="E168" s="44"/>
       <c r="F168" s="42"/>
-      <c r="G168" s="44"/>
+      <c r="G168" s="42"/>
       <c r="H168" s="44"/>
-      <c r="I168" s="42"/>
+      <c r="I168" s="44"/>
       <c r="J168" s="42"/>
       <c r="K168" s="44"/>
       <c r="L168" s="42"/>
@@ -7797,12 +7798,12 @@
       <c r="A169" s="32"/>
       <c r="B169" s="42"/>
       <c r="C169" s="42"/>
-      <c r="D169" s="44"/>
-      <c r="E169" s="42"/>
+      <c r="D169" s="42"/>
+      <c r="E169" s="44"/>
       <c r="F169" s="42"/>
-      <c r="G169" s="44"/>
+      <c r="G169" s="42"/>
       <c r="H169" s="44"/>
-      <c r="I169" s="42"/>
+      <c r="I169" s="44"/>
       <c r="J169" s="42"/>
       <c r="K169" s="44"/>
       <c r="L169" s="42"/>
@@ -7823,12 +7824,12 @@
       <c r="A170" s="32"/>
       <c r="B170" s="42"/>
       <c r="C170" s="42"/>
-      <c r="D170" s="44"/>
-      <c r="E170" s="42"/>
+      <c r="D170" s="42"/>
+      <c r="E170" s="44"/>
       <c r="F170" s="42"/>
-      <c r="G170" s="44"/>
+      <c r="G170" s="42"/>
       <c r="H170" s="44"/>
-      <c r="I170" s="42"/>
+      <c r="I170" s="44"/>
       <c r="J170" s="42"/>
       <c r="K170" s="44"/>
       <c r="L170" s="42"/>
@@ -7849,12 +7850,12 @@
       <c r="A171" s="32"/>
       <c r="B171" s="42"/>
       <c r="C171" s="42"/>
-      <c r="D171" s="44"/>
-      <c r="E171" s="42"/>
+      <c r="D171" s="42"/>
+      <c r="E171" s="44"/>
       <c r="F171" s="42"/>
-      <c r="G171" s="44"/>
+      <c r="G171" s="42"/>
       <c r="H171" s="44"/>
-      <c r="I171" s="42"/>
+      <c r="I171" s="44"/>
       <c r="J171" s="42"/>
       <c r="K171" s="44"/>
       <c r="L171" s="42"/>
@@ -7875,12 +7876,12 @@
       <c r="A172" s="32"/>
       <c r="B172" s="42"/>
       <c r="C172" s="42"/>
-      <c r="D172" s="44"/>
-      <c r="E172" s="42"/>
+      <c r="D172" s="42"/>
+      <c r="E172" s="44"/>
       <c r="F172" s="42"/>
-      <c r="G172" s="44"/>
+      <c r="G172" s="42"/>
       <c r="H172" s="44"/>
-      <c r="I172" s="42"/>
+      <c r="I172" s="44"/>
       <c r="J172" s="42"/>
       <c r="K172" s="44"/>
       <c r="L172" s="42"/>
@@ -7901,12 +7902,12 @@
       <c r="A173" s="32"/>
       <c r="B173" s="42"/>
       <c r="C173" s="42"/>
-      <c r="D173" s="44"/>
-      <c r="E173" s="42"/>
+      <c r="D173" s="42"/>
+      <c r="E173" s="44"/>
       <c r="F173" s="42"/>
-      <c r="G173" s="44"/>
+      <c r="G173" s="42"/>
       <c r="H173" s="44"/>
-      <c r="I173" s="42"/>
+      <c r="I173" s="44"/>
       <c r="J173" s="42"/>
       <c r="K173" s="44"/>
       <c r="L173" s="42"/>
@@ -7927,12 +7928,12 @@
       <c r="A174" s="32"/>
       <c r="B174" s="42"/>
       <c r="C174" s="42"/>
-      <c r="D174" s="44"/>
-      <c r="E174" s="42"/>
+      <c r="D174" s="42"/>
+      <c r="E174" s="44"/>
       <c r="F174" s="42"/>
-      <c r="G174" s="44"/>
+      <c r="G174" s="42"/>
       <c r="H174" s="44"/>
-      <c r="I174" s="42"/>
+      <c r="I174" s="44"/>
       <c r="J174" s="42"/>
       <c r="K174" s="44"/>
       <c r="L174" s="42"/>
@@ -7953,12 +7954,12 @@
       <c r="A175" s="32"/>
       <c r="B175" s="42"/>
       <c r="C175" s="42"/>
-      <c r="D175" s="44"/>
-      <c r="E175" s="42"/>
+      <c r="D175" s="42"/>
+      <c r="E175" s="44"/>
       <c r="F175" s="42"/>
-      <c r="G175" s="44"/>
+      <c r="G175" s="42"/>
       <c r="H175" s="44"/>
-      <c r="I175" s="42"/>
+      <c r="I175" s="44"/>
       <c r="J175" s="42"/>
       <c r="K175" s="44"/>
       <c r="L175" s="42"/>
@@ -7979,12 +7980,12 @@
       <c r="A176" s="32"/>
       <c r="B176" s="42"/>
       <c r="C176" s="42"/>
-      <c r="D176" s="44"/>
-      <c r="E176" s="42"/>
+      <c r="D176" s="42"/>
+      <c r="E176" s="44"/>
       <c r="F176" s="42"/>
-      <c r="G176" s="44"/>
+      <c r="G176" s="42"/>
       <c r="H176" s="44"/>
-      <c r="I176" s="42"/>
+      <c r="I176" s="44"/>
       <c r="J176" s="42"/>
       <c r="K176" s="44"/>
       <c r="L176" s="42"/>
@@ -8005,12 +8006,12 @@
       <c r="A177" s="32"/>
       <c r="B177" s="42"/>
       <c r="C177" s="42"/>
-      <c r="D177" s="44"/>
-      <c r="E177" s="42"/>
+      <c r="D177" s="42"/>
+      <c r="E177" s="44"/>
       <c r="F177" s="42"/>
-      <c r="G177" s="44"/>
+      <c r="G177" s="42"/>
       <c r="H177" s="44"/>
-      <c r="I177" s="42"/>
+      <c r="I177" s="44"/>
       <c r="J177" s="42"/>
       <c r="K177" s="44"/>
       <c r="L177" s="42"/>
@@ -8031,12 +8032,12 @@
       <c r="A178" s="32"/>
       <c r="B178" s="42"/>
       <c r="C178" s="42"/>
-      <c r="D178" s="44"/>
-      <c r="E178" s="42"/>
+      <c r="D178" s="42"/>
+      <c r="E178" s="44"/>
       <c r="F178" s="42"/>
-      <c r="G178" s="44"/>
+      <c r="G178" s="42"/>
       <c r="H178" s="44"/>
-      <c r="I178" s="42"/>
+      <c r="I178" s="44"/>
       <c r="J178" s="42"/>
       <c r="K178" s="44"/>
       <c r="L178" s="42"/>
@@ -8057,12 +8058,12 @@
       <c r="A179" s="32"/>
       <c r="B179" s="42"/>
       <c r="C179" s="42"/>
-      <c r="D179" s="44"/>
-      <c r="E179" s="42"/>
+      <c r="D179" s="42"/>
+      <c r="E179" s="44"/>
       <c r="F179" s="42"/>
-      <c r="G179" s="44"/>
+      <c r="G179" s="42"/>
       <c r="H179" s="44"/>
-      <c r="I179" s="42"/>
+      <c r="I179" s="44"/>
       <c r="J179" s="42"/>
       <c r="K179" s="44"/>
       <c r="L179" s="42"/>
@@ -8083,12 +8084,12 @@
       <c r="A180" s="32"/>
       <c r="B180" s="42"/>
       <c r="C180" s="42"/>
-      <c r="D180" s="44"/>
-      <c r="E180" s="42"/>
+      <c r="D180" s="42"/>
+      <c r="E180" s="44"/>
       <c r="F180" s="42"/>
-      <c r="G180" s="44"/>
+      <c r="G180" s="42"/>
       <c r="H180" s="44"/>
-      <c r="I180" s="42"/>
+      <c r="I180" s="44"/>
       <c r="J180" s="42"/>
       <c r="K180" s="44"/>
       <c r="L180" s="42"/>
@@ -8109,12 +8110,12 @@
       <c r="A181" s="32"/>
       <c r="B181" s="42"/>
       <c r="C181" s="42"/>
-      <c r="D181" s="44"/>
-      <c r="E181" s="42"/>
+      <c r="D181" s="42"/>
+      <c r="E181" s="44"/>
       <c r="F181" s="42"/>
-      <c r="G181" s="44"/>
+      <c r="G181" s="42"/>
       <c r="H181" s="44"/>
-      <c r="I181" s="42"/>
+      <c r="I181" s="44"/>
       <c r="J181" s="42"/>
       <c r="K181" s="44"/>
       <c r="L181" s="42"/>
@@ -8135,12 +8136,12 @@
       <c r="A182" s="32"/>
       <c r="B182" s="42"/>
       <c r="C182" s="42"/>
-      <c r="D182" s="44"/>
-      <c r="E182" s="42"/>
+      <c r="D182" s="42"/>
+      <c r="E182" s="44"/>
       <c r="F182" s="42"/>
-      <c r="G182" s="44"/>
+      <c r="G182" s="42"/>
       <c r="H182" s="44"/>
-      <c r="I182" s="42"/>
+      <c r="I182" s="44"/>
       <c r="J182" s="42"/>
       <c r="K182" s="44"/>
       <c r="L182" s="42"/>
@@ -8161,12 +8162,12 @@
       <c r="A183" s="32"/>
       <c r="B183" s="42"/>
       <c r="C183" s="42"/>
-      <c r="D183" s="44"/>
-      <c r="E183" s="42"/>
+      <c r="D183" s="42"/>
+      <c r="E183" s="44"/>
       <c r="F183" s="42"/>
-      <c r="G183" s="44"/>
+      <c r="G183" s="42"/>
       <c r="H183" s="44"/>
-      <c r="I183" s="42"/>
+      <c r="I183" s="44"/>
       <c r="J183" s="42"/>
       <c r="K183" s="44"/>
       <c r="L183" s="42"/>
@@ -8187,12 +8188,12 @@
       <c r="A184" s="32"/>
       <c r="B184" s="42"/>
       <c r="C184" s="42"/>
-      <c r="D184" s="44"/>
-      <c r="E184" s="42"/>
+      <c r="D184" s="42"/>
+      <c r="E184" s="44"/>
       <c r="F184" s="42"/>
-      <c r="G184" s="44"/>
+      <c r="G184" s="42"/>
       <c r="H184" s="44"/>
-      <c r="I184" s="42"/>
+      <c r="I184" s="44"/>
       <c r="J184" s="42"/>
       <c r="K184" s="44"/>
       <c r="L184" s="42"/>
@@ -8213,12 +8214,12 @@
       <c r="A185" s="32"/>
       <c r="B185" s="42"/>
       <c r="C185" s="42"/>
-      <c r="D185" s="44"/>
-      <c r="E185" s="42"/>
+      <c r="D185" s="42"/>
+      <c r="E185" s="44"/>
       <c r="F185" s="42"/>
-      <c r="G185" s="44"/>
+      <c r="G185" s="42"/>
       <c r="H185" s="44"/>
-      <c r="I185" s="42"/>
+      <c r="I185" s="44"/>
       <c r="J185" s="42"/>
       <c r="K185" s="44"/>
       <c r="L185" s="42"/>
@@ -8239,12 +8240,12 @@
       <c r="A186" s="32"/>
       <c r="B186" s="42"/>
       <c r="C186" s="42"/>
-      <c r="D186" s="44"/>
-      <c r="E186" s="42"/>
+      <c r="D186" s="42"/>
+      <c r="E186" s="44"/>
       <c r="F186" s="42"/>
-      <c r="G186" s="44"/>
+      <c r="G186" s="42"/>
       <c r="H186" s="44"/>
-      <c r="I186" s="42"/>
+      <c r="I186" s="44"/>
       <c r="J186" s="42"/>
       <c r="K186" s="44"/>
       <c r="L186" s="42"/>
@@ -8265,12 +8266,12 @@
       <c r="A187" s="32"/>
       <c r="B187" s="42"/>
       <c r="C187" s="42"/>
-      <c r="D187" s="44"/>
-      <c r="E187" s="42"/>
+      <c r="D187" s="42"/>
+      <c r="E187" s="44"/>
       <c r="F187" s="42"/>
-      <c r="G187" s="44"/>
+      <c r="G187" s="42"/>
       <c r="H187" s="44"/>
-      <c r="I187" s="42"/>
+      <c r="I187" s="44"/>
       <c r="J187" s="42"/>
       <c r="K187" s="44"/>
       <c r="L187" s="42"/>
@@ -8291,12 +8292,12 @@
       <c r="A188" s="32"/>
       <c r="B188" s="42"/>
       <c r="C188" s="42"/>
-      <c r="D188" s="44"/>
-      <c r="E188" s="42"/>
+      <c r="D188" s="42"/>
+      <c r="E188" s="44"/>
       <c r="F188" s="42"/>
-      <c r="G188" s="44"/>
+      <c r="G188" s="42"/>
       <c r="H188" s="44"/>
-      <c r="I188" s="42"/>
+      <c r="I188" s="44"/>
       <c r="J188" s="42"/>
       <c r="K188" s="44"/>
       <c r="L188" s="42"/>
@@ -8317,12 +8318,12 @@
       <c r="A189" s="32"/>
       <c r="B189" s="42"/>
       <c r="C189" s="42"/>
-      <c r="D189" s="44"/>
-      <c r="E189" s="42"/>
+      <c r="D189" s="42"/>
+      <c r="E189" s="44"/>
       <c r="F189" s="42"/>
-      <c r="G189" s="44"/>
+      <c r="G189" s="42"/>
       <c r="H189" s="44"/>
-      <c r="I189" s="42"/>
+      <c r="I189" s="44"/>
       <c r="J189" s="42"/>
       <c r="K189" s="44"/>
       <c r="L189" s="42"/>
@@ -8343,12 +8344,12 @@
       <c r="A190" s="32"/>
       <c r="B190" s="42"/>
       <c r="C190" s="42"/>
-      <c r="D190" s="44"/>
-      <c r="E190" s="42"/>
+      <c r="D190" s="42"/>
+      <c r="E190" s="44"/>
       <c r="F190" s="42"/>
-      <c r="G190" s="44"/>
+      <c r="G190" s="42"/>
       <c r="H190" s="44"/>
-      <c r="I190" s="42"/>
+      <c r="I190" s="44"/>
       <c r="J190" s="42"/>
       <c r="K190" s="44"/>
       <c r="L190" s="42"/>
@@ -8369,12 +8370,12 @@
       <c r="A191" s="32"/>
       <c r="B191" s="42"/>
       <c r="C191" s="42"/>
-      <c r="D191" s="44"/>
-      <c r="E191" s="42"/>
+      <c r="D191" s="42"/>
+      <c r="E191" s="44"/>
       <c r="F191" s="42"/>
-      <c r="G191" s="44"/>
+      <c r="G191" s="42"/>
       <c r="H191" s="44"/>
-      <c r="I191" s="42"/>
+      <c r="I191" s="44"/>
       <c r="J191" s="42"/>
       <c r="K191" s="44"/>
       <c r="L191" s="42"/>
@@ -8395,12 +8396,12 @@
       <c r="A192" s="32"/>
       <c r="B192" s="42"/>
       <c r="C192" s="42"/>
-      <c r="D192" s="44"/>
-      <c r="E192" s="42"/>
+      <c r="D192" s="42"/>
+      <c r="E192" s="44"/>
       <c r="F192" s="42"/>
-      <c r="G192" s="44"/>
+      <c r="G192" s="42"/>
       <c r="H192" s="44"/>
-      <c r="I192" s="42"/>
+      <c r="I192" s="44"/>
       <c r="J192" s="42"/>
       <c r="K192" s="44"/>
       <c r="L192" s="42"/>
@@ -8421,12 +8422,12 @@
       <c r="A193" s="32"/>
       <c r="B193" s="42"/>
       <c r="C193" s="42"/>
-      <c r="D193" s="44"/>
-      <c r="E193" s="42"/>
+      <c r="D193" s="42"/>
+      <c r="E193" s="44"/>
       <c r="F193" s="42"/>
-      <c r="G193" s="44"/>
+      <c r="G193" s="42"/>
       <c r="H193" s="44"/>
-      <c r="I193" s="42"/>
+      <c r="I193" s="44"/>
       <c r="J193" s="42"/>
       <c r="K193" s="44"/>
       <c r="L193" s="42"/>
@@ -8447,12 +8448,12 @@
       <c r="A194" s="32"/>
       <c r="B194" s="42"/>
       <c r="C194" s="42"/>
-      <c r="D194" s="44"/>
-      <c r="E194" s="42"/>
+      <c r="D194" s="42"/>
+      <c r="E194" s="44"/>
       <c r="F194" s="42"/>
-      <c r="G194" s="44"/>
+      <c r="G194" s="42"/>
       <c r="H194" s="44"/>
-      <c r="I194" s="42"/>
+      <c r="I194" s="44"/>
       <c r="J194" s="42"/>
       <c r="K194" s="44"/>
       <c r="L194" s="42"/>
@@ -8473,12 +8474,12 @@
       <c r="A195" s="32"/>
       <c r="B195" s="42"/>
       <c r="C195" s="42"/>
-      <c r="D195" s="44"/>
-      <c r="E195" s="42"/>
+      <c r="D195" s="42"/>
+      <c r="E195" s="44"/>
       <c r="F195" s="42"/>
-      <c r="G195" s="44"/>
+      <c r="G195" s="42"/>
       <c r="H195" s="44"/>
-      <c r="I195" s="42"/>
+      <c r="I195" s="44"/>
       <c r="J195" s="42"/>
       <c r="K195" s="44"/>
       <c r="L195" s="42"/>
@@ -8499,12 +8500,12 @@
       <c r="A196" s="32"/>
       <c r="B196" s="42"/>
       <c r="C196" s="42"/>
-      <c r="D196" s="44"/>
-      <c r="E196" s="42"/>
+      <c r="D196" s="42"/>
+      <c r="E196" s="44"/>
       <c r="F196" s="42"/>
-      <c r="G196" s="44"/>
+      <c r="G196" s="42"/>
       <c r="H196" s="44"/>
-      <c r="I196" s="42"/>
+      <c r="I196" s="44"/>
       <c r="J196" s="42"/>
       <c r="K196" s="44"/>
       <c r="L196" s="42"/>
@@ -8525,12 +8526,12 @@
       <c r="A197" s="32"/>
       <c r="B197" s="42"/>
       <c r="C197" s="42"/>
-      <c r="D197" s="44"/>
-      <c r="E197" s="42"/>
+      <c r="D197" s="42"/>
+      <c r="E197" s="44"/>
       <c r="F197" s="42"/>
-      <c r="G197" s="44"/>
+      <c r="G197" s="42"/>
       <c r="H197" s="44"/>
-      <c r="I197" s="42"/>
+      <c r="I197" s="44"/>
       <c r="J197" s="42"/>
       <c r="K197" s="44"/>
       <c r="L197" s="42"/>
@@ -8551,12 +8552,12 @@
       <c r="A198" s="32"/>
       <c r="B198" s="42"/>
       <c r="C198" s="42"/>
-      <c r="D198" s="44"/>
-      <c r="E198" s="42"/>
+      <c r="D198" s="42"/>
+      <c r="E198" s="44"/>
       <c r="F198" s="42"/>
-      <c r="G198" s="44"/>
+      <c r="G198" s="42"/>
       <c r="H198" s="44"/>
-      <c r="I198" s="42"/>
+      <c r="I198" s="44"/>
       <c r="J198" s="42"/>
       <c r="K198" s="44"/>
       <c r="L198" s="42"/>
@@ -8577,12 +8578,12 @@
       <c r="A199" s="32"/>
       <c r="B199" s="42"/>
       <c r="C199" s="42"/>
-      <c r="D199" s="44"/>
-      <c r="E199" s="42"/>
+      <c r="D199" s="42"/>
+      <c r="E199" s="44"/>
       <c r="F199" s="42"/>
-      <c r="G199" s="44"/>
+      <c r="G199" s="42"/>
       <c r="H199" s="44"/>
-      <c r="I199" s="42"/>
+      <c r="I199" s="44"/>
       <c r="J199" s="42"/>
       <c r="K199" s="44"/>
       <c r="L199" s="42"/>
@@ -8603,12 +8604,12 @@
       <c r="A200" s="32"/>
       <c r="B200" s="42"/>
       <c r="C200" s="42"/>
-      <c r="D200" s="44"/>
-      <c r="E200" s="42"/>
+      <c r="D200" s="42"/>
+      <c r="E200" s="44"/>
       <c r="F200" s="42"/>
-      <c r="G200" s="44"/>
+      <c r="G200" s="42"/>
       <c r="H200" s="44"/>
-      <c r="I200" s="42"/>
+      <c r="I200" s="44"/>
       <c r="J200" s="42"/>
       <c r="K200" s="44"/>
       <c r="L200" s="42"/>
@@ -8629,12 +8630,12 @@
       <c r="A201" s="32"/>
       <c r="B201" s="42"/>
       <c r="C201" s="42"/>
-      <c r="D201" s="44"/>
-      <c r="E201" s="42"/>
+      <c r="D201" s="42"/>
+      <c r="E201" s="44"/>
       <c r="F201" s="42"/>
-      <c r="G201" s="44"/>
+      <c r="G201" s="42"/>
       <c r="H201" s="44"/>
-      <c r="I201" s="42"/>
+      <c r="I201" s="44"/>
       <c r="J201" s="42"/>
       <c r="K201" s="44"/>
       <c r="L201" s="42"/>
@@ -8655,12 +8656,12 @@
       <c r="A202" s="32"/>
       <c r="B202" s="42"/>
       <c r="C202" s="42"/>
-      <c r="D202" s="44"/>
-      <c r="E202" s="42"/>
+      <c r="D202" s="42"/>
+      <c r="E202" s="44"/>
       <c r="F202" s="42"/>
-      <c r="G202" s="44"/>
+      <c r="G202" s="42"/>
       <c r="H202" s="44"/>
-      <c r="I202" s="42"/>
+      <c r="I202" s="44"/>
       <c r="J202" s="42"/>
       <c r="K202" s="44"/>
       <c r="L202" s="42"/>
@@ -8681,12 +8682,12 @@
       <c r="A203" s="32"/>
       <c r="B203" s="42"/>
       <c r="C203" s="42"/>
-      <c r="D203" s="44"/>
-      <c r="E203" s="42"/>
+      <c r="D203" s="42"/>
+      <c r="E203" s="44"/>
       <c r="F203" s="42"/>
-      <c r="G203" s="44"/>
+      <c r="G203" s="42"/>
       <c r="H203" s="44"/>
-      <c r="I203" s="42"/>
+      <c r="I203" s="44"/>
       <c r="J203" s="42"/>
       <c r="K203" s="44"/>
       <c r="L203" s="42"/>
@@ -8707,12 +8708,12 @@
       <c r="A204" s="32"/>
       <c r="B204" s="42"/>
       <c r="C204" s="42"/>
-      <c r="D204" s="44"/>
-      <c r="E204" s="42"/>
+      <c r="D204" s="42"/>
+      <c r="E204" s="44"/>
       <c r="F204" s="42"/>
-      <c r="G204" s="44"/>
+      <c r="G204" s="42"/>
       <c r="H204" s="44"/>
-      <c r="I204" s="42"/>
+      <c r="I204" s="44"/>
       <c r="J204" s="42"/>
       <c r="K204" s="44"/>
       <c r="L204" s="42"/>
@@ -8733,12 +8734,12 @@
       <c r="A205" s="32"/>
       <c r="B205" s="42"/>
       <c r="C205" s="42"/>
-      <c r="D205" s="44"/>
-      <c r="E205" s="42"/>
+      <c r="D205" s="42"/>
+      <c r="E205" s="44"/>
       <c r="F205" s="42"/>
-      <c r="G205" s="44"/>
+      <c r="G205" s="42"/>
       <c r="H205" s="44"/>
-      <c r="I205" s="42"/>
+      <c r="I205" s="44"/>
       <c r="J205" s="42"/>
       <c r="K205" s="44"/>
       <c r="L205" s="42"/>
@@ -8759,12 +8760,12 @@
       <c r="A206" s="32"/>
       <c r="B206" s="42"/>
       <c r="C206" s="42"/>
-      <c r="D206" s="44"/>
-      <c r="E206" s="42"/>
+      <c r="D206" s="42"/>
+      <c r="E206" s="44"/>
       <c r="F206" s="42"/>
-      <c r="G206" s="44"/>
+      <c r="G206" s="42"/>
       <c r="H206" s="44"/>
-      <c r="I206" s="42"/>
+      <c r="I206" s="44"/>
       <c r="J206" s="42"/>
       <c r="K206" s="44"/>
       <c r="L206" s="42"/>
@@ -8785,12 +8786,12 @@
       <c r="A207" s="32"/>
       <c r="B207" s="42"/>
       <c r="C207" s="42"/>
-      <c r="D207" s="44"/>
-      <c r="E207" s="42"/>
+      <c r="D207" s="42"/>
+      <c r="E207" s="44"/>
       <c r="F207" s="42"/>
-      <c r="G207" s="44"/>
+      <c r="G207" s="42"/>
       <c r="H207" s="44"/>
-      <c r="I207" s="42"/>
+      <c r="I207" s="44"/>
       <c r="J207" s="42"/>
       <c r="K207" s="44"/>
       <c r="L207" s="42"/>
@@ -8811,12 +8812,12 @@
       <c r="A208" s="32"/>
       <c r="B208" s="42"/>
       <c r="C208" s="42"/>
-      <c r="D208" s="44"/>
-      <c r="E208" s="42"/>
+      <c r="D208" s="42"/>
+      <c r="E208" s="44"/>
       <c r="F208" s="42"/>
-      <c r="G208" s="44"/>
+      <c r="G208" s="42"/>
       <c r="H208" s="44"/>
-      <c r="I208" s="42"/>
+      <c r="I208" s="44"/>
       <c r="J208" s="42"/>
       <c r="K208" s="44"/>
       <c r="L208" s="42"/>
@@ -8837,12 +8838,12 @@
       <c r="A209" s="32"/>
       <c r="B209" s="42"/>
       <c r="C209" s="42"/>
-      <c r="D209" s="44"/>
-      <c r="E209" s="42"/>
+      <c r="D209" s="42"/>
+      <c r="E209" s="44"/>
       <c r="F209" s="42"/>
-      <c r="G209" s="44"/>
+      <c r="G209" s="42"/>
       <c r="H209" s="44"/>
-      <c r="I209" s="42"/>
+      <c r="I209" s="44"/>
       <c r="J209" s="42"/>
       <c r="K209" s="44"/>
       <c r="L209" s="42"/>
@@ -8863,12 +8864,12 @@
       <c r="A210" s="32"/>
       <c r="B210" s="42"/>
       <c r="C210" s="42"/>
-      <c r="D210" s="44"/>
-      <c r="E210" s="42"/>
+      <c r="D210" s="42"/>
+      <c r="E210" s="44"/>
       <c r="F210" s="42"/>
-      <c r="G210" s="44"/>
+      <c r="G210" s="42"/>
       <c r="H210" s="44"/>
-      <c r="I210" s="42"/>
+      <c r="I210" s="44"/>
       <c r="J210" s="42"/>
       <c r="K210" s="44"/>
       <c r="L210" s="42"/>
@@ -8889,12 +8890,12 @@
       <c r="A211" s="32"/>
       <c r="B211" s="42"/>
       <c r="C211" s="42"/>
-      <c r="D211" s="44"/>
-      <c r="E211" s="42"/>
+      <c r="D211" s="42"/>
+      <c r="E211" s="44"/>
       <c r="F211" s="42"/>
-      <c r="G211" s="44"/>
+      <c r="G211" s="42"/>
       <c r="H211" s="44"/>
-      <c r="I211" s="42"/>
+      <c r="I211" s="44"/>
       <c r="J211" s="42"/>
       <c r="K211" s="44"/>
       <c r="L211" s="42"/>
@@ -8915,12 +8916,12 @@
       <c r="A212" s="32"/>
       <c r="B212" s="42"/>
       <c r="C212" s="42"/>
-      <c r="D212" s="44"/>
-      <c r="E212" s="42"/>
+      <c r="D212" s="42"/>
+      <c r="E212" s="44"/>
       <c r="F212" s="42"/>
-      <c r="G212" s="44"/>
+      <c r="G212" s="42"/>
       <c r="H212" s="44"/>
-      <c r="I212" s="42"/>
+      <c r="I212" s="44"/>
       <c r="J212" s="42"/>
       <c r="K212" s="44"/>
       <c r="L212" s="42"/>
@@ -8941,12 +8942,12 @@
       <c r="A213" s="32"/>
       <c r="B213" s="42"/>
       <c r="C213" s="42"/>
-      <c r="D213" s="44"/>
-      <c r="E213" s="42"/>
+      <c r="D213" s="42"/>
+      <c r="E213" s="44"/>
       <c r="F213" s="42"/>
-      <c r="G213" s="44"/>
+      <c r="G213" s="42"/>
       <c r="H213" s="44"/>
-      <c r="I213" s="42"/>
+      <c r="I213" s="44"/>
       <c r="J213" s="42"/>
       <c r="K213" s="44"/>
       <c r="L213" s="42"/>
@@ -8967,12 +8968,12 @@
       <c r="A214" s="32"/>
       <c r="B214" s="42"/>
       <c r="C214" s="42"/>
-      <c r="D214" s="44"/>
-      <c r="E214" s="42"/>
+      <c r="D214" s="42"/>
+      <c r="E214" s="44"/>
       <c r="F214" s="42"/>
-      <c r="G214" s="44"/>
+      <c r="G214" s="42"/>
       <c r="H214" s="44"/>
-      <c r="I214" s="42"/>
+      <c r="I214" s="44"/>
       <c r="J214" s="42"/>
       <c r="K214" s="44"/>
       <c r="L214" s="42"/>
@@ -8993,12 +8994,12 @@
       <c r="A215" s="32"/>
       <c r="B215" s="42"/>
       <c r="C215" s="42"/>
-      <c r="D215" s="44"/>
-      <c r="E215" s="42"/>
+      <c r="D215" s="42"/>
+      <c r="E215" s="44"/>
       <c r="F215" s="42"/>
-      <c r="G215" s="44"/>
+      <c r="G215" s="42"/>
       <c r="H215" s="44"/>
-      <c r="I215" s="42"/>
+      <c r="I215" s="44"/>
       <c r="J215" s="42"/>
       <c r="K215" s="44"/>
       <c r="L215" s="42"/>
@@ -9019,12 +9020,12 @@
       <c r="A216" s="32"/>
       <c r="B216" s="42"/>
       <c r="C216" s="42"/>
-      <c r="D216" s="44"/>
-      <c r="E216" s="42"/>
+      <c r="D216" s="42"/>
+      <c r="E216" s="44"/>
       <c r="F216" s="42"/>
-      <c r="G216" s="44"/>
+      <c r="G216" s="42"/>
       <c r="H216" s="44"/>
-      <c r="I216" s="42"/>
+      <c r="I216" s="44"/>
       <c r="J216" s="42"/>
       <c r="K216" s="44"/>
       <c r="L216" s="42"/>
@@ -9045,12 +9046,12 @@
       <c r="A217" s="32"/>
       <c r="B217" s="42"/>
       <c r="C217" s="42"/>
-      <c r="D217" s="44"/>
-      <c r="E217" s="42"/>
+      <c r="D217" s="42"/>
+      <c r="E217" s="44"/>
       <c r="F217" s="42"/>
-      <c r="G217" s="44"/>
+      <c r="G217" s="42"/>
       <c r="H217" s="44"/>
-      <c r="I217" s="42"/>
+      <c r="I217" s="44"/>
       <c r="J217" s="42"/>
       <c r="K217" s="44"/>
       <c r="L217" s="42"/>
@@ -9071,12 +9072,12 @@
       <c r="A218" s="32"/>
       <c r="B218" s="42"/>
       <c r="C218" s="42"/>
-      <c r="D218" s="44"/>
-      <c r="E218" s="42"/>
+      <c r="D218" s="42"/>
+      <c r="E218" s="44"/>
       <c r="F218" s="42"/>
-      <c r="G218" s="44"/>
+      <c r="G218" s="42"/>
       <c r="H218" s="44"/>
-      <c r="I218" s="42"/>
+      <c r="I218" s="44"/>
       <c r="J218" s="42"/>
       <c r="K218" s="44"/>
       <c r="L218" s="42"/>
@@ -9097,12 +9098,12 @@
       <c r="A219" s="32"/>
       <c r="B219" s="42"/>
       <c r="C219" s="42"/>
-      <c r="D219" s="44"/>
-      <c r="E219" s="42"/>
+      <c r="D219" s="42"/>
+      <c r="E219" s="44"/>
       <c r="F219" s="42"/>
-      <c r="G219" s="44"/>
+      <c r="G219" s="42"/>
       <c r="H219" s="44"/>
-      <c r="I219" s="42"/>
+      <c r="I219" s="44"/>
       <c r="J219" s="42"/>
       <c r="K219" s="44"/>
       <c r="L219" s="42"/>
@@ -9123,12 +9124,12 @@
       <c r="A220" s="32"/>
       <c r="B220" s="42"/>
       <c r="C220" s="42"/>
-      <c r="D220" s="44"/>
-      <c r="E220" s="42"/>
+      <c r="D220" s="42"/>
+      <c r="E220" s="44"/>
       <c r="F220" s="42"/>
-      <c r="G220" s="44"/>
+      <c r="G220" s="42"/>
       <c r="H220" s="44"/>
-      <c r="I220" s="42"/>
+      <c r="I220" s="44"/>
       <c r="J220" s="42"/>
       <c r="K220" s="44"/>
       <c r="L220" s="42"/>
@@ -11487,7 +11488,7 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G9">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H9">
       <formula1>"Test système"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M2:M9">
@@ -11496,7 +11497,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O2:O9">
       <formula1>"Fait,Conçu"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D9">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E9">
       <formula1>"Haute,MEDIUM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11520,8 +11521,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
+      <c r="A1" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
@@ -11554,191 +11555,191 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J3" s="5"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J4" s="5"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="10"/>
+      <c r="A5" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="17"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="15"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="22"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" s="17"/>
+      <c r="A7" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="24"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>61</v>
+      <c r="A8" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>66</v>
+      <c r="A9" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1"/>
@@ -11746,8 +11747,8 @@
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>1</v>
+      <c r="A14" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -11771,19 +11772,19 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -11792,19 +11793,19 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -11812,98 +11813,98 @@
       <c r="I17" s="5"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
+      <c r="A18" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
+      <c r="A20" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>61</v>
+      <c r="A21" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
+        <v>31</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>98</v>
+      <c r="A22" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
+        <v>31</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
@@ -12906,74 +12907,74 @@
     <row r="3" ht="15.75" customHeight="1"/>
     <row r="4" ht="15.75" customHeight="1"/>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>79</v>
+      <c r="A5" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1"/>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>81</v>
+      <c r="A7" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1"/>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>82</v>
+      <c r="A9" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1"/>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>81</v>
+      <c r="A11" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>84</v>
+      <c r="A13" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1"/>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>81</v>
+      <c r="A15" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>88</v>
+      <c r="A17" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="2" t="s">
-        <v>81</v>
+      <c r="A19" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1"/>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>89</v>
+      <c r="A21" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>81</v>
+      <c r="A23" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>91</v>
+      <c r="A25" s="3" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1"/>
